--- a/docs/Surface_全系规格与官方信源核对总账(含Ultra与官方精确直达).xlsx
+++ b/docs/Surface_全系规格与官方信源核对总账(含Ultra与官方精确直达).xlsx
@@ -101,14 +101,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF3FC"/>
-        <bgColor rgb="00EBF3FC"/>
+        <fgColor rgb="00F9FBFD"/>
+        <bgColor rgb="00F9FBFD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F9FBFD"/>
-        <bgColor rgb="00F9FBFD"/>
+        <fgColor rgb="00EBF3FC"/>
+        <bgColor rgb="00EBF3FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -170,6 +170,21 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,31 +200,13 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,10 +215,13 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:U50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Surface Pro 13 英寸 (第 12 代)</t>
+          <t>Surface Pro 13 英寸 (第 12 代) 商用版 - Intel 版</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Surface Pro, 13-inch (12th Edition)</t>
+          <t>Surface Pro, 13-inch (12th Edition) for Business - Intel</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -770,32 +770,32 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>商用/消费双通道</t>
+          <t>商用专属 (For Business)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>¥15,488 起 (骁龙版) / ¥16,888 起 (Intel Ultra 版)</t>
+          <t>¥16,888 起 (商用)</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>亮铂金、典雅黑、沙漫金</t>
+          <t>亮铂金、典雅黑</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>13.0 英寸 PixelSense™ Flow | 2880 × 1920 | 1Hz ~ 120Hz 动态自适应刷新率 (双层串联 OLED (Ultra 7 / 骁龙版标配) / 防反射超清 LCD (Ultra 5 配备))</t>
+          <t>13.0 英寸 PixelSense™ Flow | 2880 × 1920 | 1Hz ~ 120Hz 动态自适应刷新率 (防反射超清 LCD (Ultra 5) / 双层串联 OLED (Ultra 7))</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>双平台架构：英特尔® 酷睿™ Ultra 5 / Ultra 7 (第 3 代) 或 高通骁龙® X2</t>
+          <t>英特尔® 酷睿™ Ultra 5 / Ultra 7 处理器 (第 3 代)</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>50 TOPS (Intel) / 80 TOPS (骁龙)</t>
+          <t>50 TOPS</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -845,525 +845,525 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Surface Pro 13 英寸 (第 12 代) 商用版 - 骁龙版</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Surface Pro, 13-inch (12th Edition) for Business - Snapdragon</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>第 12 代 (2026) (2026)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>国行在售</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>商用专属 (For Business)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>¥15,488 起 (商用)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>13.0 英寸 PixelSense™ Flow | 2880 × 1920 | 1Hz ~ 120Hz 动态自适应刷新率 (双层串联 OLED (Tandem OLED))</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>高通骁龙 X2 (Snapdragon® X2 Elite 处理器) (12 核心)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>80 TOPS</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>16GB / 32GB / 64GB LPDDR5x | 256GB / 512GB / 1TB / 2TB 可插拔第 4 代 NVMe SSD</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>常规办公约 15 小时</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>895g (OLED 版) / 885g (LCD 版)</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>Surface Pro Flex 键盘 (蓝牙离机无线输入) | 笔协议: 10 点触控，Microsoft Pen Protocol (MPP 2.6)</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>2 × USB-C (USB4 / 雷电 4 协议兼容); 雷电: 支持 (USB4 兼容雷电 4 生态); 磁吸: 配备经典磁吸 Surface Connect 口</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Surface Pro 系列</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Surface Pro, 12 英寸 (第 1 代)</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Surface Pro, 12-inch (1st Edition)</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>第 1 代 (2026) (2026)</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>国行在售</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>商用/消费双通道</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>¥6,788 起</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>¥7,888 起 (消费版)</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>亮铂金、罗兰紫、碧海青</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>12.0 英寸 PixelSense™ 触控屏 | 2196 × 1464 | 最高 90Hz (默认 60Hz 动态切换) (PixelSense™ LCD 高清触控屏)</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>高通骁龙 X Plus (8 核心 X1P-42-100)</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>45 TOPS</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>8GB / 16GB LPDDR5x (16GB 完整解锁 Copilot+ PC 体验) | 256GB / 512GB (高速闪存)</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="O7" s="10" t="inlineStr">
         <is>
           <t>686 克 (超轻量羽量级设计)</t>
         </is>
       </c>
-      <c r="P6" s="10" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>— | 笔协议: —</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
+      <c r="Q7" s="10" t="inlineStr">
         <is>
           <t>—; 雷电: —; 磁吸: not_applicable</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R7" s="13" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S6" s="13" t="inlineStr">
+      <c r="S7" s="13" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T6" s="10" t="inlineStr">
+      <c r="T7" s="10" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr">
+      <c r="U7" s="11" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Surface Pro (第 11 代)</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Surface Pro (11th Edition)</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>第 11 代 (2024) (2024)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>国行在售</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>8,688 起</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>亮铂金、典黑、宝石蓝、砂岩金</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>13.0 英寸 PixelSense™ Flow | 2880 × 1920 | 最高 120Hz 动态自适应刷新 (OLED (X Elite) / LCD (X Plus))</t>
         </is>
       </c>
-      <c r="K7" s="15" t="inlineStr">
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>Snapdragon® X Elite / Snapdragon® X Plus</t>
         </is>
       </c>
-      <c r="L7" s="15" t="inlineStr">
+      <c r="L8" s="15" t="inlineStr">
         <is>
           <t>45 TOPS</t>
         </is>
       </c>
-      <c r="M7" s="15" t="inlineStr">
+      <c r="M8" s="15" t="inlineStr">
         <is>
           <t>16GB / 32GB LPDDR5x (8448 MT/s) | 256GB / 512GB / 1TB PCIe Gen 4</t>
         </is>
       </c>
-      <c r="N7" s="15" t="inlineStr">
+      <c r="N8" s="15" t="inlineStr">
         <is>
           <t>常规办公约 14 小时</t>
         </is>
       </c>
-      <c r="O7" s="15" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
         <is>
           <t>895g</t>
         </is>
       </c>
-      <c r="P7" s="15" t="inlineStr">
+      <c r="P8" s="15" t="inlineStr">
         <is>
           <t>Surface Pro Flex 键盘 / 特制专业键盘盖 | 笔协议: 10 点触控，支持超感触控笔触觉反馈</t>
         </is>
       </c>
-      <c r="Q7" s="15" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>2 × USB-C (USB4); 雷电: 支持 (USB4 兼容); 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R7" s="18" t="inlineStr">
+      <c r="R8" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S7" s="18" t="inlineStr">
+      <c r="S8" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T7" s="15" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U7" s="16" t="inlineStr">
+      <c r="U8" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Surface Pro 10 商用版</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Surface Pro 10 for Business</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>第 10 代商用 (2024) (2024)</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>国行在售</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>商用专属 (For Business)</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>9,888 起 (商用)</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>亮铂金、典黑</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>13.0 英寸 PixelSense™ Flow | 2880 × 1920 | 最高 120Hz (抗反射防眩光防指纹涂层 LCD)</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>Intel® Core™ Ultra 5 135U / Ultra 7 165U</t>
         </is>
       </c>
-      <c r="L8" s="10" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>11.5 TOPS</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>8GB / 16GB / 32GB / 64GB LPDDR5x | 256GB / 512GB / 1TB PCIe Gen 4</t>
         </is>
       </c>
-      <c r="N8" s="10" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>日常办公最长 19 小时</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>879g</t>
         </is>
       </c>
-      <c r="P8" s="10" t="inlineStr">
+      <c r="P9" s="20" t="inlineStr">
         <is>
           <t>Surface Pro 特制版专业键盘盖 (带 Copilot 键) | 笔协议: 10 点触控，支持超感触控笔 2</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q9" s="20" t="inlineStr">
         <is>
           <t>2 × 雷电 4 (USB-C 端口); 雷电: 原生支持 Thunderbolt 4 (40Gbps); 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="R9" s="23" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S8" s="13" t="inlineStr">
+      <c r="S9" s="23" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T8" s="10" t="inlineStr">
+      <c r="T9" s="20" t="inlineStr">
         <is>
           <t>microsoft_datasheet</t>
         </is>
       </c>
-      <c r="U8" s="11" t="inlineStr">
+      <c r="U9" s="21" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 9</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 9</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>第 9 代 (2022) (2022)</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>停止销售</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>商用/消费双通道</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>7,788 起</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>亮铂金、典黑、宝石蓝、森野绿</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>13.0 英寸 PixelSense™ Flow | 2880 × 1920 | 动态 60Hz ~ 120Hz (高素质 LCD)</t>
         </is>
       </c>
-      <c r="K9" s="10" t="inlineStr">
+      <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Intel 12代酷睿 i5-1235U / i7-1255U 或 微软 SQ® 3</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="L10" s="15" t="inlineStr">
         <is>
           <t>约 15 TOPS (SQ3 5G版)</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M10" s="15" t="inlineStr">
         <is>
           <t>8GB / 16GB / 32GB LPDDR5 | 128GB / 256GB / 512GB / 1TB SSD</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr">
+      <c r="N10" s="15" t="inlineStr">
         <is>
           <t>Intel版约 15.5 小时 / 5G版约 19 小时</t>
         </is>
       </c>
-      <c r="O9" s="10" t="inlineStr">
+      <c r="O10" s="15" t="inlineStr">
         <is>
           <t>879g (Intel) / 883g (5G版)</t>
         </is>
       </c>
-      <c r="P9" s="10" t="inlineStr">
+      <c r="P10" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 特制专业键盘盖 | 笔协议: MPP 2.0，超感笔触觉震动</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="inlineStr">
+      <c r="Q10" s="15" t="inlineStr">
         <is>
           <t>Intel版: 2 × 雷电4 / 5G版: 2 × USB-C 3.2; 雷电: Intel 版支持 Thunderbolt 4 / 5G版不支持; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="R10" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S9" s="13" t="inlineStr">
+      <c r="S10" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T9" s="10" t="inlineStr">
+      <c r="T10" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U9" s="11" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Surface Pro 系列</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Surface Pro 8</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Surface Pro 8</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>第 8 代 (2021) (2021)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>历史机型</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>商用/消费双通道</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>8,088 起</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>亮铂金、典黑</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>13.0 英寸 PixelSense™ Flow | 2880 × 1920 | 最高 120Hz (LCD)</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>Intel 第 11 代酷睿 i5-1135G7 / i7-1185G7</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>8GB / 16GB / 32GB LPDDR4x | 128GB / 256GB / 512GB / 1TB SSD</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>长达 16 小时典型使用</t>
-        </is>
-      </c>
-      <c r="O10" s="10" t="inlineStr">
-        <is>
-          <t>891g</t>
-        </is>
-      </c>
-      <c r="P10" s="10" t="inlineStr">
-        <is>
-          <t>Surface Pro 特制键盘盖 (首次采用隐藏式笔槽) | 笔协议: MPP 2.0，首次支持超感触控笔 2 触觉震动</t>
-        </is>
-      </c>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>2 × 雷电 4 (USB-C); 雷电: 原生支持 Thunderbolt 4 (40Gbps); 磁吸: 配备 Surface Connect</t>
-        </is>
-      </c>
-      <c r="R10" s="13" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S10" s="13" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T10" s="10" t="inlineStr">
-        <is>
-          <t>microsoft_official</t>
-        </is>
-      </c>
-      <c r="U10" s="11" t="inlineStr">
+      <c r="U10" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
@@ -1380,1040 +1380,1040 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
+          <t>Surface Pro 8</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Surface Pro 8</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>第 8 代 (2021) (2021)</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>历史机型</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>8,088 起</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>亮铂金、典黑</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>13.0 英寸 PixelSense™ Flow | 2880 × 1920 | 最高 120Hz (LCD)</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Intel 第 11 代酷睿 i5-1135G7 / i7-1185G7</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>8GB / 16GB / 32GB LPDDR4x | 128GB / 256GB / 512GB / 1TB SSD</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>长达 16 小时典型使用</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>891g</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>Surface Pro 特制键盘盖 (首次采用隐藏式笔槽) | 笔协议: MPP 2.0，首次支持超感触控笔 2 触觉震动</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>2 × 雷电 4 (USB-C); 雷电: 原生支持 Thunderbolt 4 (40Gbps); 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S11" s="13" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T11" s="10" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Surface Pro 系列</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
           <t>Surface Pro 7+</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Surface Pro 7+ for Business</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>第 7+ 代 (2021) (2021)</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>商用专属 (For Business)</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>6,588 起</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>亮铂金、典黑</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>12.3 英寸 PixelSense™ | 2736 × 1824 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>Intel 11代酷睿 i3-1115G4 / i5-1135G7 / i7-1165G7</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>8GB / 16GB / 32GB LPDDR4x | 128GB / 256GB / 512GB / 1TB SSD</t>
         </is>
       </c>
-      <c r="N11" s="10" t="inlineStr">
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>长达 15 小时续航</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>770g (i3/i5) / 784g (i7)</t>
         </is>
       </c>
-      <c r="P11" s="10" t="inlineStr">
+      <c r="P12" s="20" t="inlineStr">
         <is>
           <t>经典 Surface Pro 专业键盘盖 | 笔协议: 10 点触控，Surface 触控笔 (4096级压感)</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q12" s="20" t="inlineStr">
         <is>
           <t>1 × USB-C 3.1 + 1 × USB-A 3.0; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R11" s="13" t="inlineStr">
+      <c r="R12" s="23" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S11" s="13" t="inlineStr">
+      <c r="S12" s="23" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T11" s="10" t="inlineStr">
+      <c r="T12" s="20" t="inlineStr">
         <is>
           <t>microsoft_support</t>
         </is>
       </c>
-      <c r="U11" s="11" t="inlineStr">
+      <c r="U12" s="21" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Surface Pro 7</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Surface Pro 7</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>第 7 代 (2019) (2019)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>5,788 起</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>亮铂金、典黑</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>12.3 英寸 PixelSense™ | 2736 × 1824 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>Intel 10代酷睿 i3-1005G1 / i5-1035G4 / i7-1065G7</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L13" s="10" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M12" s="21" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>4GB / 8GB / 16GB LPDDR4x | 128GB / 256GB / 512GB / 1TB SSD</t>
         </is>
       </c>
-      <c r="N12" s="21" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>长达 10.5 小时日常使用</t>
         </is>
       </c>
-      <c r="O12" s="21" t="inlineStr">
+      <c r="O13" s="10" t="inlineStr">
         <is>
           <t>775g (i3/i5) / 790g (i7)</t>
         </is>
       </c>
-      <c r="P12" s="21" t="inlineStr">
+      <c r="P13" s="10" t="inlineStr">
         <is>
           <t>经典专业键盘盖 | 笔协议: 4096 级压感手写</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="Q13" s="10" t="inlineStr">
         <is>
           <t>1 × USB-C 3.1 + 1 × USB-A 3.0; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R12" s="24" t="inlineStr">
+      <c r="R13" s="13" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S12" s="24" t="inlineStr">
+      <c r="S13" s="13" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T12" s="21" t="inlineStr">
+      <c r="T13" s="10" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U12" s="25" t="inlineStr">
+      <c r="U13" s="11" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 6</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 6</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>第 6 代 (2018) (2018)</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>7,188 起</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>亮铂金、典黑</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>12.3 英寸 PixelSense™ | 2736 × 1824 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Intel 第 8 代酷睿 i5-8250U / i7-8650U</t>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr">
+      <c r="L14" s="15" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M13" s="15" t="inlineStr">
+      <c r="M14" s="15" t="inlineStr">
         <is>
           <t>8GB / 16GB LPDDR3 | 128GB / 256GB / 512GB / 1TB SSD</t>
         </is>
       </c>
-      <c r="N13" s="15" t="inlineStr">
+      <c r="N14" s="15" t="inlineStr">
         <is>
           <t>日常使用约 11 小时</t>
         </is>
       </c>
-      <c r="O13" s="15" t="inlineStr">
+      <c r="O14" s="15" t="inlineStr">
         <is>
           <t>770g (i5) / 784g (i7)</t>
         </is>
       </c>
-      <c r="P13" s="15" t="inlineStr">
+      <c r="P14" s="15" t="inlineStr">
         <is>
           <t>Alcantara 欧缔兰特制专业键盘盖 | 笔协议: MPP 触控笔与 Surface Dial 屏幕交互</t>
         </is>
       </c>
-      <c r="Q13" s="15" t="inlineStr">
+      <c r="Q14" s="15" t="inlineStr">
         <is>
           <t>1 × USB 3.0 + 1 × Mini DisplayPort; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R13" s="18" t="inlineStr">
+      <c r="R14" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S13" s="18" t="inlineStr">
+      <c r="S14" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T13" s="15" t="inlineStr">
+      <c r="T14" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U13" s="16" t="inlineStr">
+      <c r="U14" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Surface Pro (第 5 代 / 2017)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Surface Pro (5th Gen)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>第 5 代 (2017) (2017)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>5,888 起</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>12.3 英寸 PixelSense™ | 2736 × 1824 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>Intel 第 7 代酷睿 m3-7Y30 / i5-7300U / i7-7660U</t>
         </is>
       </c>
-      <c r="L14" s="21" t="inlineStr">
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M14" s="21" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>4GB / 8GB / 16GB LPDDR3 | 128GB / 256GB / 512GB / 1TB SSD</t>
         </is>
       </c>
-      <c r="N14" s="21" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>约 10 小时</t>
         </is>
       </c>
-      <c r="O14" s="21" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>768g (m3) / 770g (i5) / 782g (i7)</t>
         </is>
       </c>
-      <c r="P14" s="21" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Surface Pro 签名版 Alcantara 键盘盖 | 笔协议: 首次支持 4096 级压感与倾斜书写 (Tilt)</t>
         </is>
       </c>
-      <c r="Q14" s="21" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>1 × 全尺寸 USB 3.0 + 1 × Mini DisplayPort; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R14" s="24" t="inlineStr">
+      <c r="R15" s="13" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S14" s="24" t="inlineStr">
+      <c r="S15" s="13" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T14" s="21" t="inlineStr">
+      <c r="T15" s="10" t="inlineStr">
         <is>
           <t>microsoft_support</t>
         </is>
       </c>
-      <c r="U14" s="25" t="inlineStr">
+      <c r="U15" s="11" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 4</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 4</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>第 4 代 (2015) (2015)</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>6,688 起</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>12.3 英寸 PixelSense™ | 2736 × 1824 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Intel 第 6 代 Skylake 酷睿 m3 / i5-6300U / i7-6650U</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr">
+      <c r="L16" s="15" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M15" s="15" t="inlineStr">
+      <c r="M16" s="15" t="inlineStr">
         <is>
           <t>4GB / 8GB / 16GB | 128GB / 256GB / 512GB / 1TB SSD</t>
         </is>
       </c>
-      <c r="N15" s="15" t="inlineStr">
+      <c r="N16" s="15" t="inlineStr">
         <is>
           <t>约 7 小时</t>
         </is>
       </c>
-      <c r="O15" s="15" t="inlineStr">
+      <c r="O16" s="15" t="inlineStr">
         <is>
           <t>766g (m3) / 786g (i5/i7)</t>
         </is>
       </c>
-      <c r="P15" s="15" t="inlineStr">
+      <c r="P16" s="15" t="inlineStr">
         <is>
           <t>扩大玻璃触控板的 Pro 4 专业键盘盖 | 笔协议: 1024 级压感触控笔，顶部带实体橡皮擦</t>
         </is>
       </c>
-      <c r="Q15" s="15" t="inlineStr">
+      <c r="Q16" s="15" t="inlineStr">
         <is>
           <t>1 × USB 3.0 + 1 × Mini DisplayPort; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R15" s="18" t="inlineStr">
+      <c r="R16" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S15" s="18" t="inlineStr">
+      <c r="S16" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T15" s="15" t="inlineStr">
+      <c r="T16" s="15" t="inlineStr">
         <is>
           <t>microsoft_support</t>
         </is>
       </c>
-      <c r="U15" s="16" t="inlineStr">
+      <c r="U16" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Surface Pro 3</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Surface Pro 3</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>第 3 代 (2014) (2014)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>5,688 起</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J16" s="21" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>12.0 英寸 ClearType 黄金比例全高清屏 | 2160 × 1440 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K16" s="21" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>Intel 第 4 代 Haswell 酷睿 i3 / i5-4300U / i7-4650U</t>
         </is>
       </c>
-      <c r="L16" s="21" t="inlineStr">
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M16" s="21" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>4GB / 8GB LPDDR3 | 64GB / 128GB / 256GB / 512GB SSD</t>
         </is>
       </c>
-      <c r="N16" s="21" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>长达 9 小时网页浏览</t>
         </is>
       </c>
-      <c r="O16" s="21" t="inlineStr">
+      <c r="O17" s="10" t="inlineStr">
         <is>
           <t>800g</t>
         </is>
       </c>
-      <c r="P16" s="21" t="inlineStr">
+      <c r="P17" s="10" t="inlineStr">
         <is>
           <t>Surface Pro 3 专业键盘盖 (双折叠磁吸条) | 笔协议: 256 级压感 N-Trig 阳极氧化铝手写笔</t>
         </is>
       </c>
-      <c r="Q16" s="21" t="inlineStr">
+      <c r="Q17" s="10" t="inlineStr">
         <is>
           <t>1 × 全尺寸 USB 3.0 + 1 × Mini DisplayPort; 雷电: 否; 磁吸: 首次采用细长磁吸 Surface Connect 口</t>
         </is>
       </c>
-      <c r="R16" s="24" t="inlineStr">
+      <c r="R17" s="13" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S16" s="24" t="inlineStr">
+      <c r="S17" s="13" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T16" s="21" t="inlineStr">
+      <c r="T17" s="10" t="inlineStr">
         <is>
           <t>microsoft_support</t>
         </is>
       </c>
-      <c r="U16" s="25" t="inlineStr">
+      <c r="U17" s="11" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 2</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 2</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>第 2 代 (2013) (2013)</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>6,588 起</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>暗钛灰</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t>10.6 英寸 ClearType Full HD | 1920 × 1080 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
+      <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Intel 酷睿 i5-4200U / i5-4300U</t>
         </is>
       </c>
-      <c r="L17" s="15" t="inlineStr">
+      <c r="L18" s="15" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M17" s="15" t="inlineStr">
+      <c r="M18" s="15" t="inlineStr">
         <is>
           <t>4GB / 8GB DDR3L | 64GB / 128GB / 256GB / 512GB mSATA</t>
         </is>
       </c>
-      <c r="N17" s="15" t="inlineStr">
+      <c r="N18" s="15" t="inlineStr">
         <is>
           <t>约 6 ~ 7 小时</t>
         </is>
       </c>
-      <c r="O17" s="15" t="inlineStr">
+      <c r="O18" s="15" t="inlineStr">
         <is>
           <t>907g</t>
         </is>
       </c>
-      <c r="P17" s="15" t="inlineStr">
+      <c r="P18" s="15" t="inlineStr">
         <is>
           <t>Touch Cover 2 / Type Cover 2 | 笔协议: Wacom EMR 1024 级无源电磁手写笔 (免装电池)</t>
         </is>
       </c>
-      <c r="Q17" s="15" t="inlineStr">
+      <c r="Q18" s="15" t="inlineStr">
         <is>
           <t>1 × 全尺寸 USB 3.0 + 1 × Mini DisplayPort; 雷电: 否; 磁吸: 初代 5 针磁吸充电口</t>
         </is>
       </c>
-      <c r="R17" s="18" t="inlineStr">
+      <c r="R18" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S17" s="18" t="inlineStr">
+      <c r="S18" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T17" s="15" t="inlineStr">
+      <c r="T18" s="15" t="inlineStr">
         <is>
           <t>microsoft_support</t>
         </is>
       </c>
-      <c r="U17" s="16" t="inlineStr">
+      <c r="U18" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Surface Pro 初代 (Original)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Surface Pro (Original)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>初代 (2013) (2013)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>6,588 起</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>暗钛灰</t>
         </is>
       </c>
-      <c r="J18" s="21" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>10.6 英寸 ClearType 广视角显示屏 | 1920 × 1080 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K18" s="21" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>Intel 第 3 代酷睿 i5-3317U</t>
         </is>
       </c>
-      <c r="L18" s="21" t="inlineStr">
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M18" s="21" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>4GB DDR3 | 64GB / 128GB mSATA SSD</t>
         </is>
       </c>
-      <c r="N18" s="21" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>约 4 小时</t>
         </is>
       </c>
-      <c r="O18" s="21" t="inlineStr">
+      <c r="O19" s="10" t="inlineStr">
         <is>
           <t>907g</t>
         </is>
       </c>
-      <c r="P18" s="21" t="inlineStr">
+      <c r="P19" s="10" t="inlineStr">
         <is>
           <t>初代触控键盘 Touch Cover / 实体键盘 Type Cover | 笔协议: Wacom 压感电磁笔 (支持手掌误触抑制)</t>
         </is>
       </c>
-      <c r="Q18" s="21" t="inlineStr">
+      <c r="Q19" s="10" t="inlineStr">
         <is>
           <t>1 × 全尺寸 USB 3.0 + 1 × Mini DisplayPort; 雷电: 否; 磁吸: 初代 5 针磁吸专用充电口</t>
         </is>
       </c>
-      <c r="R18" s="24" t="inlineStr">
+      <c r="R19" s="13" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S18" s="24" t="inlineStr">
+      <c r="S19" s="13" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T18" s="21" t="inlineStr">
+      <c r="T19" s="10" t="inlineStr">
         <is>
           <t>microsoft_support</t>
         </is>
       </c>
-      <c r="U18" s="25" t="inlineStr">
+      <c r="U19" s="11" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Surface Pro 系列</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Surface Pro X</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>Surface Pro X</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Pro X 世代 (2019/2020) (2019)</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>9,988 起</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>亮铂金、典黑</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="J20" s="15" t="inlineStr">
         <is>
           <t>13.0 英寸 PixelSense™ | 2880 × 1920 | 60Hz (超薄 LCD)</t>
         </is>
       </c>
-      <c r="K19" s="15" t="inlineStr">
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Microsoft SQ® 1 / SQ® 2</t>
         </is>
       </c>
-      <c r="L19" s="15" t="inlineStr">
+      <c r="L20" s="15" t="inlineStr">
         <is>
           <t>约 9 TOPS</t>
         </is>
       </c>
-      <c r="M19" s="15" t="inlineStr">
+      <c r="M20" s="15" t="inlineStr">
         <is>
           <t>8GB / 16GB LPDDR4x | 128GB / 256GB / 512GB 可拆卸 NVMe SSD</t>
         </is>
       </c>
-      <c r="N19" s="15" t="inlineStr">
+      <c r="N20" s="15" t="inlineStr">
         <is>
           <t>长达 15 小时全天续航</t>
         </is>
       </c>
-      <c r="O19" s="15" t="inlineStr">
+      <c r="O20" s="15" t="inlineStr">
         <is>
           <t>774g</t>
         </is>
       </c>
-      <c r="P19" s="15" t="inlineStr">
+      <c r="P20" s="15" t="inlineStr">
         <is>
           <t>Surface Pro X 特制签名版键盘盖 | 笔协议: 首创 Slim Pen 细扁笔与无线笔槽补电</t>
         </is>
       </c>
-      <c r="Q19" s="15" t="inlineStr">
+      <c r="Q20" s="15" t="inlineStr">
         <is>
           <t>2 × USB-C 3.2 Gen 2; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R19" s="18" t="inlineStr">
+      <c r="R20" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S19" s="18" t="inlineStr">
+      <c r="S20" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T19" s="15" t="inlineStr">
+      <c r="T20" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U19" s="16" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Surface Laptop 系列</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Surface Laptop 13.8 英寸 (第 8 代)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Surface Laptop, 13.8-inch (8th Edition)</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>第 8 代 (2026) (2026)</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>国行在售</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>商用/消费双通道</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>¥14,888 起 (骁龙版) / ¥16,888 起 (Intel Ultra 版)</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>亮铂金、典黑、宝石蓝、沙漫金</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>13.8 英寸 PixelSense™ Flow | 2304 × 1536 | 120Hz 动态刷新率 (Dynamic Refresh) (超清圆角窄边框触控屏)</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>双平台架构：英特尔® 酷睿™ Ultra 5 / Ultra 7 (第 3 代) 或 高通骁龙® X2</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>50 TOPS (Intel) / 80 TOPS (骁龙)</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>16GB / 32GB / 64GB LPDDR5x (8533 MT/s) | 512GB / 1TB / 2TB PCIe Gen 4 NVMe</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>1340 克</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>— | 笔协议: —</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>—; 雷电: —; 磁吸: 1 × Surface Connect 磁吸专用充电接口</t>
-        </is>
-      </c>
-      <c r="R20" s="8" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S20" s="8" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>microsoft_official</t>
-        </is>
-      </c>
-      <c r="U20" s="6" t="inlineStr">
+      <c r="U20" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Surface Laptop 15 英寸 (第 8 代)</t>
+          <t>Surface Laptop 13.8 英寸 (第 8 代) 商用版 - Intel 版</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Surface Laptop, 15-inch (8th Edition)</t>
+          <t>Surface Laptop, 13.8-inch (8th Edition) for Business - Intel</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2450,390 +2450,390 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>商用/消费双通道</t>
+          <t>商用专属 (For Business)</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>¥16,888 起 (Intel Ultra 版) / ¥15,888 起 (骁龙版)</t>
+          <t>¥16,888 起 (商用)</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>亮铂金、典黑</t>
+          <t>亮铂金、典雅黑</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
+          <t>13.8 英寸 PixelSense™ Flow | 2304 × 1536 | 120Hz 动态刷新率 (Dynamic Refresh) (超清圆角窄边框触控屏)</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>英特尔® 酷睿™ Ultra 5 / Ultra 7 处理器 (第 3 代)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>50 TOPS</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>16GB / 32GB / 64GB LPDDR5x (8533 MT/s) | 512GB / 1TB / 2TB PCIe Gen 4 NVMe</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>1340 克</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>— | 笔协议: —</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>—; 雷电: —; 磁吸: 1 × Surface Connect 磁吸专用充电接口</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U21" s="6" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Surface Laptop 系列</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Surface Laptop 13.8 英寸 (第 8 代) 商用版 - 骁龙版</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Surface Laptop, 13.8-inch (8th Edition) for Business - Snapdragon</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>第 8 代 (2026) (2026)</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>国行在售</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>商用专属 (For Business)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>¥14,888 起 (商用)</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>13.8 英寸 PixelSense™ Flow | 2304 × 1536 | 120Hz 动态刷新率 (Dynamic Refresh) (超清圆角窄边框触控屏)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>高通骁龙 X2 (Snapdragon® X2 Elite 处理器) (12 核心)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>80 TOPS</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>16GB / 32GB / 64GB LPDDR5x (8533 MT/s) | 512GB / 1TB / 2TB PCIe Gen 4 NVMe</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>1340 克</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>— | 笔协议: —</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>—; 雷电: —; 磁吸: 1 × Surface Connect 磁吸专用充电接口</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U22" s="6" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Surface Laptop 系列</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Surface Laptop 15 英寸 (第 8 代) 商用版 - Intel 版</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Surface Laptop, 15-inch (8th Edition) for Business - Intel</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>第 8 代 (2026) (2026)</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>国行在售</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>商用专属 (For Business)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>¥18,888 起 (商用)</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
           <t>15.0 英寸 PixelSense™ Flow | 2496 × 1664 | 最高 120Hz 动态自适应刷新 (超视网膜 LCD)</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>双平台架构：英特尔® 酷睿™ Ultra 5 / Ultra 7 (第 3 代) 或 高通骁龙® X2</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>50 TOPS (Intel) / 80 TOPS (骁龙)</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>英特尔® 酷睿™ Ultra X7 处理器 (第 3 代)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>50 TOPS</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>16GB / 32GB / 64GB LPDDR5x | 512GB / 1TB / 2TB PCIe Gen 4 SSD</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>常规办公长达 18 小时</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>1660g (1.66 kg)</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>一体式键盘 | 笔协议: 10 点触控 (不支持手写笔)</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>2 × USB-C (USB4) + 1 × USB-A 3.1 + MicroSD 卡槽; 雷电: 支持 (USB4 兼容); 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R21" s="8" t="inlineStr">
+      <c r="R23" s="8" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S21" s="8" t="inlineStr">
+      <c r="S23" s="8" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T21" s="5" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
+      <c r="U23" s="6" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Surface Laptop 系列</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>Surface Laptop (第 7 代) 13.8 英寸</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>Surface Laptop (7th Edition)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>第 7 代 (2024) (2024)</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Surface Laptop 15 英寸 (第 8 代) 商用版 - 骁龙版</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Surface Laptop, 15-inch (8th Edition) for Business - Snapdragon</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>第 8 代 (2026) (2026)</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>国行在售</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>消费级零售</t>
-        </is>
-      </c>
-      <c r="H22" s="23" t="inlineStr">
-        <is>
-          <t>8,688 起</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>亮铂金、典黑、宝石蓝、砂岩金</t>
-        </is>
-      </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>13.8 英寸 PixelSense™ Flow | 2304 × 1536 | 最高 120Hz 动态自适应 (抗反射高光泽 LCD)</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>高通 Snapdragon® X Elite / Snapdragon® X Plus</t>
-        </is>
-      </c>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t>45 TOPS</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
-        <is>
-          <t>16GB / 32GB LPDDR5x | 256GB / 512GB / 1TB SSD</t>
-        </is>
-      </c>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t>网页浏览约 13 小时</t>
-        </is>
-      </c>
-      <c r="O22" s="21" t="inlineStr">
-        <is>
-          <t>1340g</t>
-        </is>
-      </c>
-      <c r="P22" s="21" t="inlineStr">
-        <is>
-          <t>一体式键盘 (带 Copilot 键) | 笔协议: 10 点触控 (不支持手写笔)</t>
-        </is>
-      </c>
-      <c r="Q22" s="21" t="inlineStr">
-        <is>
-          <t>2 × USB-C (USB4) + 1 × USB-A 3.1; 雷电: 支持 (USB4 兼容); 磁吸: 配备 Surface Connect</t>
-        </is>
-      </c>
-      <c r="R22" s="24" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>商用专属 (For Business)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>¥16,888 起 (商用)</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>15.0 英寸 PixelSense™ Flow | 2496 × 1664 | 最高 120Hz 动态自适应刷新 (超视网膜 LCD)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>高通骁龙 X2 (Snapdragon® X2 Elite 处理器) (12 核心)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>80 TOPS</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>16GB / 32GB / 64GB LPDDR5x | 512GB / 1TB / 2TB PCIe Gen 4 SSD</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>常规办公长达 18 小时</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>1660g (1.66 kg)</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>一体式键盘 | 笔协议: 10 点触控 (不支持手写笔)</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>2 × USB-C (USB4) + 1 × USB-A 3.1 + MicroSD 卡槽; 雷电: 支持 (USB4 兼容); 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S22" s="24" t="inlineStr">
+      <c r="S24" s="8" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T22" s="21" t="inlineStr">
+      <c r="T24" s="5" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U22" s="25" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Surface Laptop 系列</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Surface Laptop 6 商用版 (13.5" &amp; 15")</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Surface Laptop 6 for Business</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>第 6 代商用 (2024) (2024)</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>国行在售</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>商用专属 (For Business)</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>9,988 起</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>亮铂金、典黑</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>13.5 英寸 / 15.0 英寸 PixelSense™ | 2256 × 1504 (13.5") / 2496 × 1664 (15") | 60Hz (防眩光抗反射涂层 LCD)</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>Intel® Core™ Ultra 5 135H / Ultra 7 165H</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>11.5 TOPS</t>
-        </is>
-      </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>8GB / 16GB / 32GB / 64GB LPDDR5x | 256GB / 512GB / 1TB SSD</t>
-        </is>
-      </c>
-      <c r="N23" s="10" t="inlineStr">
-        <is>
-          <t>长达 18.5 ~ 19 小时</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>1380g (13.5") / 1680g (15")</t>
-        </is>
-      </c>
-      <c r="P23" s="10" t="inlineStr">
-        <is>
-          <t>背光键盘 + 机械触控板 | 笔协议: 10 点触控，支持手写笔</t>
-        </is>
-      </c>
-      <c r="Q23" s="10" t="inlineStr">
-        <is>
-          <t>13.5寸: 1×雷电4 + 1×USB-A / 15寸: 2×雷电4 + 1×USB-A; 雷电: 原生支持 Thunderbolt 4 (40Gbps); 磁吸: 配备 Surface Connect</t>
-        </is>
-      </c>
-      <c r="R23" s="13" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S23" s="13" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T23" s="10" t="inlineStr">
-        <is>
-          <t>microsoft_datasheet</t>
-        </is>
-      </c>
-      <c r="U23" s="11" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Surface Laptop 系列</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Surface Laptop 5 (13.5" &amp; 15")</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Surface Laptop 5</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>第 5 代 (2022) (2022)</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>停止销售</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>商用/消费双通道</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>7,888 起</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>亮铂金、典黑、森野绿、砂岩金</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>13.5 英寸 / 15.0 英寸 PixelSense™ | 2256 × 1504 (13.5") / 2496 × 1664 (15") | 60Hz (LCD)</t>
-        </is>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>Intel 12 代酷睿 i5-1235U / i7-1255U</t>
-        </is>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="M24" s="10" t="inlineStr">
-        <is>
-          <t>8GB / 16GB / 32GB LPDDR5x | 256GB / 512GB / 1TB SSD</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="inlineStr">
-        <is>
-          <t>最长 18 小时 (13.5") / 17 小时 (15")</t>
-        </is>
-      </c>
-      <c r="O24" s="10" t="inlineStr">
-        <is>
-          <t>1272g (欧缔兰) / 1297g (金属) / 1560g (15寸)</t>
-        </is>
-      </c>
-      <c r="P24" s="10" t="inlineStr">
-        <is>
-          <t>Alcantara 或金属掌托舒适背光键盘 | 笔协议: 10 点触控，支持手写笔</t>
-        </is>
-      </c>
-      <c r="Q24" s="10" t="inlineStr">
-        <is>
-          <t>1 × 雷电 4 (USB-C) + 1 × USB-A 3.1; 雷电: 原生支持 Thunderbolt 4 (40Gbps); 磁吸: 配备 Surface Connect</t>
-        </is>
-      </c>
-      <c r="R24" s="13" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S24" s="13" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T24" s="10" t="inlineStr">
-        <is>
-          <t>microsoft_official</t>
-        </is>
-      </c>
-      <c r="U24" s="11" t="inlineStr">
+      <c r="U24" s="6" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
@@ -2850,620 +2850,620 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
+          <t>Surface Laptop (第 7 代) 13.8 英寸</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop (7th Edition)</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>第 7 代 (2024) (2024)</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>国行在售</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>8,688 起</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>亮铂金、典黑、宝石蓝、砂岩金</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>13.8 英寸 PixelSense™ Flow | 2304 × 1536 | 最高 120Hz 动态自适应 (抗反射高光泽 LCD)</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>高通 Snapdragon® X Elite / Snapdragon® X Plus</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>45 TOPS</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>16GB / 32GB LPDDR5x | 256GB / 512GB / 1TB SSD</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>网页浏览约 13 小时</t>
+        </is>
+      </c>
+      <c r="O25" s="10" t="inlineStr">
+        <is>
+          <t>1340g</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>一体式键盘 (带 Copilot 键) | 笔协议: 10 点触控 (不支持手写笔)</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>2 × USB-C (USB4) + 1 × USB-A 3.1; 雷电: 支持 (USB4 兼容); 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R25" s="13" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S25" s="13" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T25" s="10" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U25" s="11" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Surface Laptop 系列</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>Surface Laptop 6 商用版 (13.5" &amp; 15")</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Surface Laptop 6 for Business</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>第 6 代商用 (2024) (2024)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>国行在售</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>商用专属 (For Business)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>9,988 起</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>亮铂金、典黑</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>13.5 英寸 / 15.0 英寸 PixelSense™ | 2256 × 1504 (13.5") / 2496 × 1664 (15") | 60Hz (防眩光抗反射涂层 LCD)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>Intel® Core™ Ultra 5 135H / Ultra 7 165H</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>11.5 TOPS</t>
+        </is>
+      </c>
+      <c r="M26" s="20" t="inlineStr">
+        <is>
+          <t>8GB / 16GB / 32GB / 64GB LPDDR5x | 256GB / 512GB / 1TB SSD</t>
+        </is>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>长达 18.5 ~ 19 小时</t>
+        </is>
+      </c>
+      <c r="O26" s="20" t="inlineStr">
+        <is>
+          <t>1380g (13.5") / 1680g (15")</t>
+        </is>
+      </c>
+      <c r="P26" s="20" t="inlineStr">
+        <is>
+          <t>背光键盘 + 机械触控板 | 笔协议: 10 点触控，支持手写笔</t>
+        </is>
+      </c>
+      <c r="Q26" s="20" t="inlineStr">
+        <is>
+          <t>13.5寸: 1×雷电4 + 1×USB-A / 15寸: 2×雷电4 + 1×USB-A; 雷电: 原生支持 Thunderbolt 4 (40Gbps); 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R26" s="23" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S26" s="23" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T26" s="20" t="inlineStr">
+        <is>
+          <t>microsoft_datasheet</t>
+        </is>
+      </c>
+      <c r="U26" s="21" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Surface Laptop 系列</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop 5 (13.5" &amp; 15")</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop 5</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>第 5 代 (2022) (2022)</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>停止销售</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>7,888 起</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>亮铂金、典黑、森野绿、砂岩金</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>13.5 英寸 / 15.0 英寸 PixelSense™ | 2256 × 1504 (13.5") / 2496 × 1664 (15") | 60Hz (LCD)</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>Intel 12 代酷睿 i5-1235U / i7-1255U</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>8GB / 16GB / 32GB LPDDR5x | 256GB / 512GB / 1TB SSD</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>最长 18 小时 (13.5") / 17 小时 (15")</t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>1272g (欧缔兰) / 1297g (金属) / 1560g (15寸)</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="inlineStr">
+        <is>
+          <t>Alcantara 或金属掌托舒适背光键盘 | 笔协议: 10 点触控，支持手写笔</t>
+        </is>
+      </c>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>1 × 雷电 4 (USB-C) + 1 × USB-A 3.1; 雷电: 原生支持 Thunderbolt 4 (40Gbps); 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R27" s="13" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S27" s="13" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T27" s="10" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U27" s="11" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Surface Laptop 系列</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
           <t>Surface Laptop 4 (13.5" &amp; 15")</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>Surface Laptop 4</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>第 4 代 (2021) (2021)</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>商用/消费双通道</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>7,888 起</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>亮铂金、典黑、冰晶蓝、砂岩金</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="J28" s="15" t="inlineStr">
         <is>
           <t>13.5 英寸 / 15.0 英寸 PixelSense™ | 2256 × 1504 (13.5") / 2496 × 1664 (15") | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="K28" s="15" t="inlineStr">
         <is>
           <t>Intel 11 代酷睿 或 AMD Ryzen™ 5 4680U / 7 4980U 微软定制版</t>
         </is>
       </c>
-      <c r="L25" s="10" t="inlineStr">
+      <c r="L28" s="15" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr">
+      <c r="M28" s="15" t="inlineStr">
         <is>
           <t>8GB / 16GB / 32GB LPDDR4x | 256GB / 512GB / 1TB SSD</t>
         </is>
       </c>
-      <c r="N25" s="10" t="inlineStr">
+      <c r="N28" s="15" t="inlineStr">
         <is>
           <t>长达 19 小时 (AMD 版) / 17 小时 (Intel 版)</t>
         </is>
       </c>
-      <c r="O25" s="10" t="inlineStr">
+      <c r="O28" s="15" t="inlineStr">
         <is>
           <t>1265g (欧缔兰) / 1288g (金属) / 1542g (15寸)</t>
         </is>
       </c>
-      <c r="P25" s="10" t="inlineStr">
+      <c r="P28" s="15" t="inlineStr">
         <is>
           <t>1.3mm 键程背光键盘 | 笔协议: 10 点触控，支持触控笔</t>
         </is>
       </c>
-      <c r="Q25" s="10" t="inlineStr">
+      <c r="Q28" s="15" t="inlineStr">
         <is>
           <t>1 × USB-C 3.2 + 1 × USB-A 3.1; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R25" s="13" t="inlineStr">
+      <c r="R28" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S25" s="13" t="inlineStr">
+      <c r="S28" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T25" s="10" t="inlineStr">
+      <c r="T28" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U25" s="11" t="inlineStr">
+      <c r="U28" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Surface Laptop 系列</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Surface Laptop 3 (13.5" &amp; 15")</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Surface Laptop 3</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>第 3 代 (2019) (2019)</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F29" s="25" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>商用/消费双通道</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>7,888 起</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>亮铂金、典黑、砂岩金、钴蓝色</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>13.5 英寸 / 15.0 英寸 (首款 15 寸轻薄本) | 2256 × 1504 (13.5") / 2496 × 1664 (15") | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K26" s="10" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>Intel 10 代 10nm 酷睿 或 AMD Ryzen™ 5 3580U / 7 3780U 微软定制版</t>
         </is>
       </c>
-      <c r="L26" s="10" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>8GB / 16GB / 32GB DDR4 | 128GB / 256GB / 512GB / 1TB SSD</t>
         </is>
       </c>
-      <c r="N26" s="10" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>长达 11.5 小时典型续航 (支持 1小时快充80%)</t>
         </is>
       </c>
-      <c r="O26" s="10" t="inlineStr">
+      <c r="O29" s="10" t="inlineStr">
         <is>
           <t>1265g (欧缔兰) / 1288g (金属) / 1542g (15寸)</t>
         </is>
       </c>
-      <c r="P26" s="10" t="inlineStr">
+      <c r="P29" s="10" t="inlineStr">
         <is>
           <t>大尺寸玻璃触控板 + 静音键盘 | 笔协议: 10 点触控，支持手写笔</t>
         </is>
       </c>
-      <c r="Q26" s="10" t="inlineStr">
+      <c r="Q29" s="10" t="inlineStr">
         <is>
           <t>1 × USB-C 3.1 + 1 × USB-A 3.0; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R26" s="13" t="inlineStr">
+      <c r="R29" s="13" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S26" s="13" t="inlineStr">
+      <c r="S29" s="13" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T26" s="10" t="inlineStr">
+      <c r="T29" s="10" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U26" s="11" t="inlineStr">
+      <c r="U29" s="11" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Surface Laptop 系列</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>Surface Laptop 2</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>Surface Laptop 2</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>第 2 代 (2018) (2018)</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>7,888 起</t>
         </is>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="I30" s="15" t="inlineStr">
         <is>
           <t>亮铂金、典黑、勃艮第红、深钴蓝</t>
         </is>
       </c>
-      <c r="J27" s="15" t="inlineStr">
+      <c r="J30" s="15" t="inlineStr">
         <is>
           <t>13.5 英寸 PixelSense™ | 2256 × 1504 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K27" s="15" t="inlineStr">
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>Intel 第 8 代酷睿 i5-8250U / i7-8650U</t>
         </is>
       </c>
-      <c r="L27" s="15" t="inlineStr">
+      <c r="L30" s="15" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M27" s="15" t="inlineStr">
+      <c r="M30" s="15" t="inlineStr">
         <is>
           <t>8GB / 16GB LPDDR3 | 128GB / 256GB / 512GB / 1TB SSD</t>
         </is>
       </c>
-      <c r="N27" s="15" t="inlineStr">
+      <c r="N30" s="15" t="inlineStr">
         <is>
           <t>约 10 小时</t>
         </is>
       </c>
-      <c r="O27" s="15" t="inlineStr">
+      <c r="O30" s="15" t="inlineStr">
         <is>
           <t>1252g (i5) / 1283g (i7)</t>
         </is>
       </c>
-      <c r="P27" s="15" t="inlineStr">
+      <c r="P30" s="15" t="inlineStr">
         <is>
           <t>欧缔兰 Alcantara 顶级织物静音键盘 | 笔协议: 10 点触控，支持触控笔</t>
         </is>
       </c>
-      <c r="Q27" s="15" t="inlineStr">
+      <c r="Q30" s="15" t="inlineStr">
         <is>
           <t>1 × 全尺寸 USB 3.0 + 1 × Mini DisplayPort; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R27" s="18" t="inlineStr">
+      <c r="R30" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S27" s="18" t="inlineStr">
+      <c r="S30" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T27" s="15" t="inlineStr">
+      <c r="T30" s="15" t="inlineStr">
         <is>
           <t>microsoft_support</t>
         </is>
       </c>
-      <c r="U27" s="16" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Surface Laptop 系列</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>Surface Laptop 初代 (Original)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>Surface Laptop (Original)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>初代 (2017) (2017)</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>历史机型</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>消费级零售</t>
-        </is>
-      </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>7,688 起</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="inlineStr">
-        <is>
-          <t>亮铂金、石墨金、勃艮第红、深钴蓝</t>
-        </is>
-      </c>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t>13.5 英寸 PixelSense™ (超薄触摸屏模组) | 2256 × 1504 | 60Hz (LCD)</t>
-        </is>
-      </c>
-      <c r="K28" s="21" t="inlineStr">
-        <is>
-          <t>Intel 第 7 代酷睿 i5-7200U / i7-7660U</t>
-        </is>
-      </c>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="M28" s="21" t="inlineStr">
-        <is>
-          <t>4GB / 8GB / 16GB LPDDR3 | 128GB / 256GB / 512GB / 1TB SSD</t>
-        </is>
-      </c>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t>约 10 小时</t>
-        </is>
-      </c>
-      <c r="O28" s="21" t="inlineStr">
-        <is>
-          <t>1252g (i5) / 1283g (i7)</t>
-        </is>
-      </c>
-      <c r="P28" s="21" t="inlineStr">
-        <is>
-          <t>Alcantara 奢华织物背光键盘 | 笔协议: 10 点触控，支持 Surface 触控笔</t>
-        </is>
-      </c>
-      <c r="Q28" s="21" t="inlineStr">
-        <is>
-          <t>1 × 全尺寸 USB 3.0 + 1 × Mini DisplayPort; 雷电: 否; 磁吸: 配备 Surface Connect</t>
-        </is>
-      </c>
-      <c r="R28" s="24" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S28" s="24" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T28" s="21" t="inlineStr">
-        <is>
-          <t>microsoft_support</t>
-        </is>
-      </c>
-      <c r="U28" s="25" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Surface Laptop Studio 系列</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Surface Laptop Studio 2</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Surface Laptop Studio 2</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>第 2 代 (2023) (2023)</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>国行在售</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>商用专属 (For Business)</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>19,588 起</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>亮铂金</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>14.4 英寸 PixelSense™ Flow | 2400 × 1600 | 高达 120Hz 动态自适应高刷 (超高对比度广色域 LCD)</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Intel 第 13 代酷睿 i7-13700H</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>约 10 TOPS (Windows Studio 特效专用)</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>16GB / 32GB / 64GB LPDDR5x | 512GB / 1TB / 2TB Gen 4 NVMe SSD</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>常规办公约 18 小时 (集显) / 15 小时 (独显)</t>
-        </is>
-      </c>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>1980g (集显) / 2000g (RTX 4050) / 2010g (RTX 4060)</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>大面积触觉反馈触控板 + 沉浸背光键盘 | 笔协议: 超感笔触觉反馈，屏幕内置触觉震动马达</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>2 × 雷电 4 (USB-C) + 1 × USB-A 3.1 + MicroSD 卡槽; 雷电: 原生支持 Thunderbolt 4 (40Gbps); 磁吸: 配备 Surface Connect</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>microsoft_official</t>
-        </is>
-      </c>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Surface Laptop Studio 系列</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Surface Laptop Studio 初代</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Surface Laptop Studio (Original)</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>初代 (2021) (2021)</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>历史机型</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>商用/消费双通道</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>12,888 起</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>亮铂金</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>14.4 英寸 PixelSense™ Flow | 2400 × 1600 | 最高 120Hz 刷新率 (LCD)</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>Intel 11代酷睿 H35 i5-11300H / i7-11370H</t>
-        </is>
-      </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>16GB / 32GB LPDDR4x | 256GB / 512GB / 1TB / 2TB SSD</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="inlineStr">
-        <is>
-          <t>长达 19 小时 (i5) / 18 小时 (i7)</t>
-        </is>
-      </c>
-      <c r="O30" s="10" t="inlineStr">
-        <is>
-          <t>1742g (i5) / 1820g (i7)</t>
-        </is>
-      </c>
-      <c r="P30" s="10" t="inlineStr">
-        <is>
-          <t>全新大尺寸触觉反馈触控板 + 背光键盘 | 笔协议: MPP 2.0，Slim Pen 2 触觉震动</t>
-        </is>
-      </c>
-      <c r="Q30" s="10" t="inlineStr">
-        <is>
-          <t>2 × 雷电 4 (USB-C); 雷电: 原生支持 Thunderbolt 4; 磁吸: 配备 Surface Connect</t>
-        </is>
-      </c>
-      <c r="R30" s="13" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S30" s="13" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T30" s="10" t="inlineStr">
-        <is>
-          <t>microsoft_support</t>
-        </is>
-      </c>
-      <c r="U30" s="11" t="inlineStr">
+      <c r="U30" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
@@ -3475,1465 +3475,1465 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
+          <t>Surface Laptop 系列</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop 初代 (Original)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop (Original)</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>初代 (2017) (2017)</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>历史机型</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>7,688 起</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>亮铂金、石墨金、勃艮第红、深钴蓝</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>13.5 英寸 PixelSense™ (超薄触摸屏模组) | 2256 × 1504 | 60Hz (LCD)</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>Intel 第 7 代酷睿 i5-7200U / i7-7660U</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>4GB / 8GB / 16GB LPDDR3 | 128GB / 256GB / 512GB / 1TB SSD</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>约 10 小时</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>1252g (i5) / 1283g (i7)</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr">
+        <is>
+          <t>Alcantara 奢华织物背光键盘 | 笔协议: 10 点触控，支持 Surface 触控笔</t>
+        </is>
+      </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>1 × 全尺寸 USB 3.0 + 1 × Mini DisplayPort; 雷电: 否; 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R31" s="13" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S31" s="13" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T31" s="10" t="inlineStr">
+        <is>
+          <t>microsoft_support</t>
+        </is>
+      </c>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Surface Laptop Studio 系列</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Surface Laptop Studio 2</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Surface Laptop Studio 2</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>第 2 代 (2023) (2023)</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>国行在售</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>商用专属 (For Business)</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>19,588 起</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>亮铂金</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>14.4 英寸 PixelSense™ Flow | 2400 × 1600 | 高达 120Hz 动态自适应高刷 (超高对比度广色域 LCD)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Intel 第 13 代酷睿 i7-13700H</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>约 10 TOPS (Windows Studio 特效专用)</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>16GB / 32GB / 64GB LPDDR5x | 512GB / 1TB / 2TB Gen 4 NVMe SSD</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>常规办公约 18 小时 (集显) / 15 小时 (独显)</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>1980g (集显) / 2000g (RTX 4050) / 2010g (RTX 4060)</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>大面积触觉反馈触控板 + 沉浸背光键盘 | 笔协议: 超感笔触觉反馈，屏幕内置触觉震动马达</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>2 × 雷电 4 (USB-C) + 1 × USB-A 3.1 + MicroSD 卡槽; 雷电: 原生支持 Thunderbolt 4 (40Gbps); 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U32" s="6" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>Surface Laptop Studio 系列</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>Surface Laptop Studio 初代</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>Surface Laptop Studio (Original)</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>初代 (2021) (2021)</t>
+        </is>
+      </c>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>历史机型</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
+        <is>
+          <t>商用/消费双通道</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>12,888 起</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>亮铂金</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>14.4 英寸 PixelSense™ Flow | 2400 × 1600 | 最高 120Hz 刷新率 (LCD)</t>
+        </is>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>Intel 11代酷睿 H35 i5-11300H / i7-11370H</t>
+        </is>
+      </c>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="M33" s="20" t="inlineStr">
+        <is>
+          <t>16GB / 32GB LPDDR4x | 256GB / 512GB / 1TB / 2TB SSD</t>
+        </is>
+      </c>
+      <c r="N33" s="20" t="inlineStr">
+        <is>
+          <t>长达 19 小时 (i5) / 18 小时 (i7)</t>
+        </is>
+      </c>
+      <c r="O33" s="20" t="inlineStr">
+        <is>
+          <t>1742g (i5) / 1820g (i7)</t>
+        </is>
+      </c>
+      <c r="P33" s="20" t="inlineStr">
+        <is>
+          <t>全新大尺寸触觉反馈触控板 + 背光键盘 | 笔协议: MPP 2.0，Slim Pen 2 触觉震动</t>
+        </is>
+      </c>
+      <c r="Q33" s="20" t="inlineStr">
+        <is>
+          <t>2 × 雷电 4 (USB-C); 雷电: 原生支持 Thunderbolt 4; 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R33" s="23" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S33" s="23" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T33" s="20" t="inlineStr">
+        <is>
+          <t>microsoft_support</t>
+        </is>
+      </c>
+      <c r="U33" s="21" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
           <t>Surface Go 系列</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>Surface Go 4 商用版</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>Surface Go 4 for Business</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E34" s="19" t="inlineStr">
         <is>
           <t>第 4 代 (2023) (2023)</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>国行在售</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>商用专属 (For Business)</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>4,588 起</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>10.5 英寸 PixelSense™ 显示屏 | 1920 × 1280 | 60Hz (康宁大猩猩玻璃 3 LCD)</t>
         </is>
       </c>
-      <c r="K31" s="10" t="inlineStr">
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t>Intel® 处理器 N200</t>
         </is>
       </c>
-      <c r="L31" s="10" t="inlineStr">
+      <c r="L34" s="20" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="M34" s="20" t="inlineStr">
         <is>
           <t>8GB LPDDR5 (全系标配 8G 淘汰前代短板) | 64GB UFS / 128GB / 256GB SSD</t>
         </is>
       </c>
-      <c r="N31" s="10" t="inlineStr">
+      <c r="N34" s="20" t="inlineStr">
         <is>
           <t>典型日常使用长达 12.5 小时</t>
         </is>
       </c>
-      <c r="O31" s="10" t="inlineStr">
+      <c r="O34" s="20" t="inlineStr">
         <is>
           <t>521g (羽量级口袋平板)</t>
         </is>
       </c>
-      <c r="P31" s="10" t="inlineStr">
+      <c r="P34" s="20" t="inlineStr">
         <is>
           <t>Surface Go 专业键盘盖 (欧缔兰或黑色) | 笔协议: 10 点触控，支持 Surface 触控笔</t>
         </is>
       </c>
-      <c r="Q31" s="10" t="inlineStr">
+      <c r="Q34" s="20" t="inlineStr">
         <is>
           <t>1 × USB-C 3.1 + MicroSD 卡槽; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R31" s="13" t="inlineStr">
+      <c r="R34" s="23" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S31" s="13" t="inlineStr">
+      <c r="S34" s="23" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T31" s="10" t="inlineStr">
+      <c r="T34" s="20" t="inlineStr">
         <is>
           <t>microsoft_datasheet</t>
         </is>
       </c>
-      <c r="U31" s="11" t="inlineStr">
+      <c r="U34" s="21" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Surface Go 系列</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Surface Go 3</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Surface Go 3</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>第 3 代 (2021) (2021)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>2,988 起</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>亮铂金、典黑</t>
         </is>
       </c>
-      <c r="J32" s="21" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>10.5 英寸 PixelSense™ | 1920 × 1280 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K32" s="21" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>Intel 奔腾金牌 6500Y / 酷睿 i3-10100Y</t>
         </is>
       </c>
-      <c r="L32" s="21" t="inlineStr">
+      <c r="L35" s="10" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M32" s="21" t="inlineStr">
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>4GB / 8GB LPDDR3 | 64GB eMMC / 128GB SSD</t>
         </is>
       </c>
-      <c r="N32" s="21" t="inlineStr">
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>长达 11 小时日常使用</t>
         </is>
       </c>
-      <c r="O32" s="21" t="inlineStr">
+      <c r="O35" s="10" t="inlineStr">
         <is>
           <t>544g (Wi-Fi) / 553g (LTE)</t>
         </is>
       </c>
-      <c r="P32" s="21" t="inlineStr">
+      <c r="P35" s="10" t="inlineStr">
         <is>
           <t>Surface Go 专业键盘盖 | 笔协议: 4096 级压感手写</t>
         </is>
       </c>
-      <c r="Q32" s="21" t="inlineStr">
+      <c r="Q35" s="10" t="inlineStr">
         <is>
           <t>1 × USB-C + MicroSD 卡槽; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R32" s="24" t="inlineStr">
+      <c r="R35" s="13" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S32" s="24" t="inlineStr">
+      <c r="S35" s="13" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T32" s="21" t="inlineStr">
+      <c r="T35" s="10" t="inlineStr">
         <is>
           <t>microsoft_support</t>
         </is>
       </c>
-      <c r="U32" s="25" t="inlineStr">
+      <c r="U35" s="11" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="14" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>Surface Laptop Go 系列</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>Surface Laptop Go 3</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>Surface Laptop Go 3</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>第 3 代 (2023) (2023)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>国行在售</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>5,888 起</t>
         </is>
       </c>
-      <c r="I33" s="15" t="inlineStr">
+      <c r="I36" s="15" t="inlineStr">
         <is>
           <t>亮铂金、冰晶蓝、砂岩金、仙野绿</t>
         </is>
       </c>
-      <c r="J33" s="15" t="inlineStr">
+      <c r="J36" s="15" t="inlineStr">
         <is>
           <t>12.4 英寸 PixelSense™ 触控屏 | 1536 × 1024 | 60Hz (LCD)</t>
         </is>
       </c>
-      <c r="K33" s="15" t="inlineStr">
+      <c r="K36" s="15" t="inlineStr">
         <is>
           <t>Intel 第 12 代酷睿 i5-1235U</t>
         </is>
       </c>
-      <c r="L33" s="15" t="inlineStr">
+      <c r="L36" s="15" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M33" s="15" t="inlineStr">
+      <c r="M36" s="15" t="inlineStr">
         <is>
           <t>8GB / 16GB LPDDR5 (全系标配 8G 起步) | 256GB / 512GB SSD</t>
         </is>
       </c>
-      <c r="N33" s="15" t="inlineStr">
+      <c r="N36" s="15" t="inlineStr">
         <is>
           <t>长达 15 小时典型使用</t>
         </is>
       </c>
-      <c r="O33" s="15" t="inlineStr">
+      <c r="O36" s="15" t="inlineStr">
         <is>
           <t>1130g (1.13 kg 极轻办公本)</t>
         </is>
       </c>
-      <c r="P33" s="15" t="inlineStr">
+      <c r="P36" s="15" t="inlineStr">
         <is>
           <t>全尺寸 1.3mm 键程键盘 (无背光) | 笔协议: 10 点触控 (注意：不支持手写笔)</t>
         </is>
       </c>
-      <c r="Q33" s="15" t="inlineStr">
+      <c r="Q36" s="15" t="inlineStr">
         <is>
           <t>1 × USB-C 3.2 + 1 × USB-A 3.1; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R33" s="18" t="inlineStr">
+      <c r="R36" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S33" s="18" t="inlineStr">
+      <c r="S36" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T33" s="15" t="inlineStr">
+      <c r="T36" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U33" s="16" t="inlineStr">
+      <c r="U36" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Surface Studio / Hub 系列</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Surface Studio 2+</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Surface Studio 2+</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Studio 2+ (2022) (2022)</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>国行在售</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>商用专属 (For Business)</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>35,888 起</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>28.0 英寸 PixelSense™ 超高清巨幕 | 4500 × 3000 (1350 万像素, 1:1 物理比例) | 60Hz (DCI-P3 广色域专业显示器)</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>Intel 第 11 代酷睿 H35 i7-11370H</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>32GB DDR4 | 1TB 固态硬盘 NVMe SSD</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>not_applicable (台式一体机插电运行)</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>9560g (9.56 kg 配重基座)</t>
         </is>
       </c>
-      <c r="P34" s="5" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>随附 Surface 蓝牙键盘、精密鼠标、触控笔 | 笔协议: 10 点触控，支持手写笔与 Surface Dial 屏上旋钮</t>
         </is>
       </c>
-      <c r="Q34" s="5" t="inlineStr">
+      <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>3 × 雷电 4 (USB-C) + 2 × USB-A 3.1 + RJ45 千兆网口; 雷电: 原生支持 3 个 Thunderbolt 4 端口; 磁吸: not_applicable (标准 AC 交流电输入)</t>
         </is>
       </c>
-      <c r="R34" s="8" t="inlineStr">
+      <c r="R37" s="8" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S34" s="8" t="inlineStr">
+      <c r="S37" s="8" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T34" s="5" t="inlineStr">
+      <c r="T37" s="5" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U34" s="6" t="inlineStr">
+      <c r="U37" s="6" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="14" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Surface Duo 系列</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>Surface Duo 2</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>Surface Duo 2</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>第 2 代 (2021) (2021)</t>
         </is>
       </c>
-      <c r="F35" s="26" t="inlineStr">
+      <c r="F38" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>11,988 起</t>
         </is>
       </c>
-      <c r="I35" s="15" t="inlineStr">
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>冰川白、曜石黑</t>
         </is>
       </c>
-      <c r="J35" s="15" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t>单屏 5.8 英寸 AMOLED × 2 / 展开共 8.3 英寸 | 展开 2688 × 1892 | 动态 90Hz 自适应刷新 (双曲面柔性 AMOLED)</t>
         </is>
       </c>
-      <c r="K35" s="15" t="inlineStr">
+      <c r="K38" s="15" t="inlineStr">
         <is>
           <t>高通骁龙™ 888 5G 旗舰平台</t>
         </is>
       </c>
-      <c r="L35" s="15" t="inlineStr">
+      <c r="L38" s="15" t="inlineStr">
         <is>
           <t>26 TOPS</t>
         </is>
       </c>
-      <c r="M35" s="15" t="inlineStr">
+      <c r="M38" s="15" t="inlineStr">
         <is>
           <t>8GB LPDDR5 | 128GB / 256GB / 512GB UFS 3.1</t>
         </is>
       </c>
-      <c r="N35" s="15" t="inlineStr">
+      <c r="N38" s="15" t="inlineStr">
         <is>
           <t>通话 28 小时</t>
         </is>
       </c>
-      <c r="O35" s="15" t="inlineStr">
+      <c r="O38" s="15" t="inlineStr">
         <is>
           <t>284g (折叠双屏手机)</t>
         </is>
       </c>
-      <c r="P35" s="15" t="inlineStr">
+      <c r="P38" s="15" t="inlineStr">
         <is>
           <t>屏幕虚拟双屏键盘 / 蓝牙外接 | 笔协议: 支持 Surface Slim Pen 2 手写</t>
         </is>
       </c>
-      <c r="Q35" s="15" t="inlineStr">
+      <c r="Q38" s="15" t="inlineStr">
         <is>
           <t>1 × USB-C 3.2 Gen 2 (支持 DP 4K 输出); 雷电: 否; 磁吸: not_applicable</t>
         </is>
       </c>
-      <c r="R35" s="18" t="inlineStr">
+      <c r="R38" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S35" s="18" t="inlineStr">
+      <c r="S38" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T35" s="15" t="inlineStr">
+      <c r="T38" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U35" s="16" t="inlineStr">
+      <c r="U38" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Surface Book 系列</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Surface Book 3 15 英寸</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Surface Book 3 15-inch</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>第 3 代 (2020) (2020)</t>
         </is>
       </c>
-      <c r="F36" s="27" t="inlineStr">
+      <c r="F39" s="27" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>商用专属 (For Business)</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>18,288 起</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>15.0 英寸 PixelSense™ 触控屏 | 3240 × 2160 | 60Hz (高精触控 LCD 显示面板)</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>Intel® 第 10 代酷睿™ i7-1065G7</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>16GB / 32GB LPDDR4x (3733 MT/s) | 256GB / 512GB / 1TB / 2TB PCIe NVMe SSD</t>
         </is>
       </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>常规使用长达 17.5 小时</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>1905g (含底座 1.9kg / 单平板部分 817g)</t>
         </is>
       </c>
-      <c r="P36" s="5" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr">
         <is>
           <t>全尺寸背光独立物理键盘 (带动力肌肉解耦锁) | 笔协议: 10 点触控，支持 Surface 触控笔与 Surface Dial 屏上交互</t>
         </is>
       </c>
-      <c r="Q36" s="5" t="inlineStr">
+      <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>2 × USB-A 3.1 Gen 2 + 1 × USB-C 3.1 Gen 2 (支持 USB-PD); 雷电: 否; 磁吸: 配备 2 个 Surface Connect (屏幕底座各 1 个)</t>
         </is>
       </c>
-      <c r="R36" s="8" t="inlineStr">
+      <c r="R39" s="8" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S36" s="8" t="inlineStr">
+      <c r="S39" s="8" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T36" s="5" t="inlineStr">
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U36" s="6" t="inlineStr">
+      <c r="U39" s="6" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="14" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>Surface Book 系列</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Surface Book 3 13.5 英寸</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>Surface Book 3 13.5-inch</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>第 3 代 (2020) (2020)</t>
         </is>
       </c>
-      <c r="F37" s="26" t="inlineStr">
+      <c r="F40" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="H40" s="17" t="inlineStr">
         <is>
           <t>12,888 起</t>
         </is>
       </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J37" s="15" t="inlineStr">
+      <c r="J40" s="15" t="inlineStr">
         <is>
           <t>13.5 英寸 PixelSense™ 触控屏 | 3000 × 2000 | 60Hz (LCD 高精度触控屏)</t>
         </is>
       </c>
-      <c r="K37" s="15" t="inlineStr">
+      <c r="K40" s="15" t="inlineStr">
         <is>
           <t>Intel® 第 10 代酷睿™ i5-1035G7 / i7-1065G7</t>
         </is>
       </c>
-      <c r="L37" s="15" t="inlineStr">
+      <c r="L40" s="15" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M37" s="15" t="inlineStr">
+      <c r="M40" s="15" t="inlineStr">
         <is>
           <t>8GB / 16GB / 32GB LPDDR4x | 256GB / 512GB / 1TB PCIe NVMe SSD</t>
         </is>
       </c>
-      <c r="N37" s="15" t="inlineStr">
+      <c r="N40" s="15" t="inlineStr">
         <is>
           <t>长达 15.5 小时典型使用</t>
         </is>
       </c>
-      <c r="O37" s="15" t="inlineStr">
+      <c r="O40" s="15" t="inlineStr">
         <is>
           <t>1534g (集显) / 1642g (独显) / 平板 718g</t>
         </is>
       </c>
-      <c r="P37" s="15" t="inlineStr">
+      <c r="P40" s="15" t="inlineStr">
         <is>
           <t>全尺寸背光物理键盘 | 笔协议: 10 点触控，支持 MPP 协议手写笔</t>
         </is>
       </c>
-      <c r="Q37" s="15" t="inlineStr">
+      <c r="Q40" s="15" t="inlineStr">
         <is>
           <t>2 × USB-A 3.1 + 1 × USB-C 3.1 + SD 卡槽; 雷电: 否; 磁吸: 配备 2 个 Surface Connect 端口</t>
         </is>
       </c>
-      <c r="R37" s="18" t="inlineStr">
+      <c r="R40" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S37" s="18" t="inlineStr">
+      <c r="S40" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T37" s="15" t="inlineStr">
+      <c r="T40" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U37" s="16" t="inlineStr">
+      <c r="U40" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Surface Book 系列</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Surface Book 2 15 英寸</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>Surface Book 2 15-inch</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>第 2 代 (2017) (2017)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F41" s="25" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G38" s="20" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H38" s="23" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>19,888 起</t>
         </is>
       </c>
-      <c r="I38" s="21" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J38" s="21" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>15.0 英寸 PixelSense™ 显示屏 | 3240 × 2160 | 60Hz (LCD 触控屏)</t>
         </is>
       </c>
-      <c r="K38" s="21" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>Intel® 第 8 代酷睿™ i7-8650U</t>
         </is>
       </c>
-      <c r="L38" s="21" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M38" s="21" t="inlineStr">
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>16GB LPDDR3 (1866 MT/s) | 256GB / 512GB / 1TB PCIe NVMe SSD</t>
         </is>
       </c>
-      <c r="N38" s="21" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>视频播放长达 17 小时</t>
         </is>
       </c>
-      <c r="O38" s="21" t="inlineStr">
+      <c r="O41" s="10" t="inlineStr">
         <is>
           <t>1905g (含底座)</t>
         </is>
       </c>
-      <c r="P38" s="21" t="inlineStr">
+      <c r="P41" s="10" t="inlineStr">
         <is>
           <t>全尺寸背光物理键盘 | 笔协议: 10 点触控，支持 Surface Pen 4096 级压感</t>
         </is>
       </c>
-      <c r="Q38" s="21" t="inlineStr">
+      <c r="Q41" s="10" t="inlineStr">
         <is>
           <t>2 × USB-A 3.1 + 1 × USB-C 3.1 Gen 1 + SDXC 卡槽; 雷电: 否; 磁吸: 配备 2 个 Surface Connect</t>
         </is>
       </c>
-      <c r="R38" s="24" t="inlineStr">
+      <c r="R41" s="13" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S38" s="24" t="inlineStr">
+      <c r="S41" s="13" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T38" s="21" t="inlineStr">
+      <c r="T41" s="10" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U38" s="25" t="inlineStr">
+      <c r="U41" s="11" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="14" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>Surface Book 系列</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>Surface Book 初代 (Original)</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>Surface Book (1st Gen)</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>初代 (2015) (2015)</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="F42" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
+      <c r="H42" s="17" t="inlineStr">
         <is>
           <t>11,088 起</t>
         </is>
       </c>
-      <c r="I39" s="15" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J39" s="15" t="inlineStr">
+      <c r="J42" s="15" t="inlineStr">
         <is>
           <t>13.5 英寸 PixelSense™ 触控屏 | 3000 × 2000 | 60Hz (LCD 光学触控贴合屏)</t>
         </is>
       </c>
-      <c r="K39" s="15" t="inlineStr">
+      <c r="K42" s="15" t="inlineStr">
         <is>
           <t>Intel® 第 6 代酷睿™ i5-6300U / i7-6600U</t>
         </is>
       </c>
-      <c r="L39" s="15" t="inlineStr">
+      <c r="L42" s="15" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M39" s="15" t="inlineStr">
+      <c r="M42" s="15" t="inlineStr">
         <is>
           <t>8GB / 16GB LPDDR3 | 128GB / 256GB / 512GB / 1TB PCIe SSD</t>
         </is>
       </c>
-      <c r="N39" s="15" t="inlineStr">
+      <c r="N42" s="15" t="inlineStr">
         <is>
           <t>常规视频播放长达 12 小时</t>
         </is>
       </c>
-      <c r="O39" s="15" t="inlineStr">
+      <c r="O42" s="15" t="inlineStr">
         <is>
           <t>1516g (独显款 1576g / 单屏幕仅 726g)</t>
         </is>
       </c>
-      <c r="P39" s="15" t="inlineStr">
+      <c r="P42" s="15" t="inlineStr">
         <is>
           <t>全尺寸背光机械锁键盘底座 | 笔协议: 10 点触控，配备初代磁吸 Surface Pen (1024级压感)</t>
         </is>
       </c>
-      <c r="Q39" s="15" t="inlineStr">
+      <c r="Q42" s="15" t="inlineStr">
         <is>
           <t>2 × USB-A 3.0 + Mini DisplayPort + SD 卡槽; 雷电: 否; 磁吸: 配备 2 个 Surface Connect 端口</t>
         </is>
       </c>
-      <c r="R39" s="18" t="inlineStr">
+      <c r="R42" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S39" s="18" t="inlineStr">
+      <c r="S42" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T39" s="15" t="inlineStr">
+      <c r="T42" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U39" s="16" t="inlineStr">
+      <c r="U42" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="20" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Surface Go 系列</t>
         </is>
       </c>
-      <c r="C40" s="21" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Surface Go 2</t>
         </is>
       </c>
-      <c r="D40" s="21" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>Surface Go 2</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>第 2 代 (2020) (2020)</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F43" s="25" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G40" s="20" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H40" s="23" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>2,988 起</t>
         </is>
       </c>
-      <c r="I40" s="21" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J40" s="21" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>10.5 英寸 PixelSense™ 显示屏 | 1920 × 1280 | 60Hz (康宁大猩猩玻璃 3 LCD)</t>
         </is>
       </c>
-      <c r="K40" s="21" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>Intel® Core™ m3-8100Y / Pentium® Gold 4425Y</t>
         </is>
       </c>
-      <c r="L40" s="21" t="inlineStr">
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M40" s="21" t="inlineStr">
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>4GB / 8GB LPDDR3 | 64GB eMMC / 128GB SSD</t>
         </is>
       </c>
-      <c r="N40" s="21" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>常规日常使用长达 10 小时</t>
         </is>
       </c>
-      <c r="O40" s="21" t="inlineStr">
+      <c r="O43" s="10" t="inlineStr">
         <is>
           <t>544g (Wi-Fi 版) / 553g (LTE 版)</t>
         </is>
       </c>
-      <c r="P40" s="21" t="inlineStr">
+      <c r="P43" s="10" t="inlineStr">
         <is>
           <t>Surface Go 专业键盘盖 | 笔协议: 10 点触控，支持 Surface 触控笔 4096 级压感</t>
         </is>
       </c>
-      <c r="Q40" s="21" t="inlineStr">
+      <c r="Q43" s="10" t="inlineStr">
         <is>
           <t>1 × USB-C + 1 × MicroSDXC 卡槽; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R40" s="24" t="inlineStr">
+      <c r="R43" s="13" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S40" s="24" t="inlineStr">
+      <c r="S43" s="13" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T40" s="21" t="inlineStr">
+      <c r="T43" s="10" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U40" s="25" t="inlineStr">
+      <c r="U43" s="11" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="14" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="14" t="inlineStr">
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>Surface Go 系列</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>Surface Go 初代 (Original)</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>Surface Go (1st Gen)</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
         <is>
           <t>初代 (2018) (2018)</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="F44" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="H44" s="17" t="inlineStr">
         <is>
           <t>2,988 起</t>
         </is>
       </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="I44" s="15" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J41" s="15" t="inlineStr">
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t>10.0 英寸 PixelSense™ 显示屏 | 1800 × 1200 | 60Hz (康宁大猩猩玻璃 3 LCD)</t>
         </is>
       </c>
-      <c r="K41" s="15" t="inlineStr">
+      <c r="K44" s="15" t="inlineStr">
         <is>
           <t>Intel® Pentium® Gold 4415Y</t>
         </is>
       </c>
-      <c r="L41" s="15" t="inlineStr">
+      <c r="L44" s="15" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M41" s="15" t="inlineStr">
+      <c r="M44" s="15" t="inlineStr">
         <is>
           <t>4GB / 8GB LPDDR3 | 64GB eMMC / 128GB SSD</t>
         </is>
       </c>
-      <c r="N41" s="15" t="inlineStr">
+      <c r="N44" s="15" t="inlineStr">
         <is>
           <t>本地视频播放长达 9 小时</t>
         </is>
       </c>
-      <c r="O41" s="15" t="inlineStr">
+      <c r="O44" s="15" t="inlineStr">
         <is>
           <t>522g (极其轻便)</t>
         </is>
       </c>
-      <c r="P41" s="15" t="inlineStr">
+      <c r="P44" s="15" t="inlineStr">
         <is>
           <t>Surface Go 专业键盘盖 | 笔协议: 10 点触控，支持 Surface Pen 4096 级压感</t>
         </is>
       </c>
-      <c r="Q41" s="15" t="inlineStr">
+      <c r="Q44" s="15" t="inlineStr">
         <is>
           <t>1 × USB-C 3.1 + 1 × MicroSDXC 卡槽; 雷电: 否; 磁吸: 配备 Surface Connect</t>
         </is>
       </c>
-      <c r="R41" s="18" t="inlineStr">
+      <c r="R44" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S41" s="18" t="inlineStr">
+      <c r="S44" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T41" s="15" t="inlineStr">
+      <c r="T44" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U41" s="16" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>Surface Laptop Go 系列</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>Surface Laptop Go 2</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>Surface Laptop Go 2</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="inlineStr">
-        <is>
-          <t>第 2 代 (2022) (2022)</t>
-        </is>
-      </c>
-      <c r="F42" s="22" t="inlineStr">
-        <is>
-          <t>历史机型</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>消费级零售</t>
-        </is>
-      </c>
-      <c r="H42" s="23" t="inlineStr">
-        <is>
-          <t>5,188 起</t>
-        </is>
-      </c>
-      <c r="I42" s="21" t="inlineStr">
-        <is>
-          <t>仙踪绿、冰晶蓝、砂岩金、亮铂金</t>
-        </is>
-      </c>
-      <c r="J42" s="21" t="inlineStr">
-        <is>
-          <t>12.4 英寸 PixelSense™ 触控屏 | 1536 × 1024 | 60Hz (LCD 触控屏)</t>
-        </is>
-      </c>
-      <c r="K42" s="21" t="inlineStr">
-        <is>
-          <t>Intel® 第 11 代酷睿™ i5-1135G7</t>
-        </is>
-      </c>
-      <c r="L42" s="21" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="M42" s="21" t="inlineStr">
-        <is>
-          <t>4GB / 8GB / 16GB LPDDR4x | 128GB / 256GB SSD</t>
-        </is>
-      </c>
-      <c r="N42" s="21" t="inlineStr">
-        <is>
-          <t>典型日常使用长达 13.5 小时</t>
-        </is>
-      </c>
-      <c r="O42" s="21" t="inlineStr">
-        <is>
-          <t>1127g (1.12 kg 超轻量轻薄本)</t>
-        </is>
-      </c>
-      <c r="P42" s="21" t="inlineStr">
-        <is>
-          <t>全尺寸 1.3mm 舒适键程键盘 (无背光) | 笔协议: 10 点触控 (不支持手写笔)</t>
-        </is>
-      </c>
-      <c r="Q42" s="21" t="inlineStr">
-        <is>
-          <t>1 × USB-C 3.2 + 1 × USB-A 3.1; 雷电: 否; 磁吸: 配备 Surface Connect</t>
-        </is>
-      </c>
-      <c r="R42" s="24" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S42" s="24" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T42" s="21" t="inlineStr">
-        <is>
-          <t>microsoft_official</t>
-        </is>
-      </c>
-      <c r="U42" s="25" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="14" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>Surface Laptop Go 系列</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Surface Laptop Go 初代</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>Surface Laptop Go (1st Gen)</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>初代 (2020) (2020)</t>
-        </is>
-      </c>
-      <c r="F43" s="26" t="inlineStr">
-        <is>
-          <t>历史机型</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>消费级零售</t>
-        </is>
-      </c>
-      <c r="H43" s="17" t="inlineStr">
-        <is>
-          <t>4,388 起</t>
-        </is>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>冰晶蓝、砂岩金、亮铂金</t>
-        </is>
-      </c>
-      <c r="J43" s="15" t="inlineStr">
-        <is>
-          <t>12.4 英寸 PixelSense™ 触控屏 | 1536 × 1024 | 60Hz (LCD 触控屏)</t>
-        </is>
-      </c>
-      <c r="K43" s="15" t="inlineStr">
-        <is>
-          <t>Intel® 第 10 代酷睿™ i5-1035G1</t>
-        </is>
-      </c>
-      <c r="L43" s="15" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="M43" s="15" t="inlineStr">
-        <is>
-          <t>4GB / 8GB LPDDR4x | 64GB eMMC / 128GB / 256GB SSD</t>
-        </is>
-      </c>
-      <c r="N43" s="15" t="inlineStr">
-        <is>
-          <t>长达 13 小时典型日常使用</t>
-        </is>
-      </c>
-      <c r="O43" s="15" t="inlineStr">
-        <is>
-          <t>1110g (1.11 kg 极轻办公本)</t>
-        </is>
-      </c>
-      <c r="P43" s="15" t="inlineStr">
-        <is>
-          <t>全尺寸键盘 (无背光) | 笔协议: 10 点触控 (不支持手写笔)</t>
-        </is>
-      </c>
-      <c r="Q43" s="15" t="inlineStr">
-        <is>
-          <t>1 × USB-C + 1 × USB-A; 雷电: 否; 磁吸: 配备 Surface Connect</t>
-        </is>
-      </c>
-      <c r="R43" s="18" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S43" s="18" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T43" s="15" t="inlineStr">
-        <is>
-          <t>microsoft_official</t>
-        </is>
-      </c>
-      <c r="U43" s="16" t="inlineStr">
-        <is>
-          <t>✅ 100% 官方已核验</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Surface Studio / Hub 系列</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>Surface Studio 2</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>Surface Studio 2</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>第 2 代 (2018) (2018)</t>
-        </is>
-      </c>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>历史机型</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>商用专属 (For Business)</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>29,888 起</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>亮铂金配重底座</t>
-        </is>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>28.0 英寸 PixelSense™ 巨幅触控显示屏 | 4500 × 3000 (1350 万像素) | 60Hz (真实比例 13.5 亿色超薄 IPS 显示屏)</t>
-        </is>
-      </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>Intel® 第 7 代酷睿™ i7-7820HQ</t>
-        </is>
-      </c>
-      <c r="L44" s="10" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>16GB / 32GB DDR4 (2400 MT/s) | 1TB / 2TB PCIe NVMe SSD</t>
-        </is>
-      </c>
-      <c r="N44" s="10" t="inlineStr">
-        <is>
-          <t>持续交流电源连接</t>
-        </is>
-      </c>
-      <c r="O44" s="10" t="inlineStr">
-        <is>
-          <t>9560g (9.56 kg)</t>
-        </is>
-      </c>
-      <c r="P44" s="10" t="inlineStr">
-        <is>
-          <t>配备 Surface 蓝牙键盘与精准鼠标 | 笔协议: 10 点触控，支持 Surface 触控笔 (4096级压感) 与 Surface Dial</t>
-        </is>
-      </c>
-      <c r="Q44" s="10" t="inlineStr">
-        <is>
-          <t>4 × USB-A 3.0 + 1 × USB-C + 千兆以太网口 + SD 卡槽; 雷电: 否; 磁吸: not_applicable</t>
-        </is>
-      </c>
-      <c r="R44" s="13" t="inlineStr">
-        <is>
-          <t>点击进入商城选配 ↗</t>
-        </is>
-      </c>
-      <c r="S44" s="13" t="inlineStr">
-        <is>
-          <t>点击查阅架构白皮书 ↗</t>
-        </is>
-      </c>
-      <c r="T44" s="10" t="inlineStr">
-        <is>
-          <t>microsoft_official</t>
-        </is>
-      </c>
-      <c r="U44" s="11" t="inlineStr">
+      <c r="U44" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
@@ -4945,310 +4945,625 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
+          <t>Surface Laptop Go 系列</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop Go 2</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop Go 2</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>第 2 代 (2022) (2022)</t>
+        </is>
+      </c>
+      <c r="F45" s="25" t="inlineStr">
+        <is>
+          <t>历史机型</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>5,188 起</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>仙踪绿、冰晶蓝、砂岩金、亮铂金</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>12.4 英寸 PixelSense™ 触控屏 | 1536 × 1024 | 60Hz (LCD 触控屏)</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>Intel® 第 11 代酷睿™ i5-1135G7</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>4GB / 8GB / 16GB LPDDR4x | 128GB / 256GB SSD</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>典型日常使用长达 13.5 小时</t>
+        </is>
+      </c>
+      <c r="O45" s="10" t="inlineStr">
+        <is>
+          <t>1127g (1.12 kg 超轻量轻薄本)</t>
+        </is>
+      </c>
+      <c r="P45" s="10" t="inlineStr">
+        <is>
+          <t>全尺寸 1.3mm 舒适键程键盘 (无背光) | 笔协议: 10 点触控 (不支持手写笔)</t>
+        </is>
+      </c>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>1 × USB-C 3.2 + 1 × USB-A 3.1; 雷电: 否; 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S45" s="13" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T45" s="10" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Surface Laptop Go 系列</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Surface Laptop Go 初代</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Surface Laptop Go (1st Gen)</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>初代 (2020) (2020)</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>历史机型</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>消费级零售</t>
+        </is>
+      </c>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>4,388 起</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>冰晶蓝、砂岩金、亮铂金</t>
+        </is>
+      </c>
+      <c r="J46" s="15" t="inlineStr">
+        <is>
+          <t>12.4 英寸 PixelSense™ 触控屏 | 1536 × 1024 | 60Hz (LCD 触控屏)</t>
+        </is>
+      </c>
+      <c r="K46" s="15" t="inlineStr">
+        <is>
+          <t>Intel® 第 10 代酷睿™ i5-1035G1</t>
+        </is>
+      </c>
+      <c r="L46" s="15" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="M46" s="15" t="inlineStr">
+        <is>
+          <t>4GB / 8GB LPDDR4x | 64GB eMMC / 128GB / 256GB SSD</t>
+        </is>
+      </c>
+      <c r="N46" s="15" t="inlineStr">
+        <is>
+          <t>长达 13 小时典型日常使用</t>
+        </is>
+      </c>
+      <c r="O46" s="15" t="inlineStr">
+        <is>
+          <t>1110g (1.11 kg 极轻办公本)</t>
+        </is>
+      </c>
+      <c r="P46" s="15" t="inlineStr">
+        <is>
+          <t>全尺寸键盘 (无背光) | 笔协议: 10 点触控 (不支持手写笔)</t>
+        </is>
+      </c>
+      <c r="Q46" s="15" t="inlineStr">
+        <is>
+          <t>1 × USB-C + 1 × USB-A; 雷电: 否; 磁吸: 配备 Surface Connect</t>
+        </is>
+      </c>
+      <c r="R46" s="18" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S46" s="18" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T46" s="15" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U46" s="16" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
           <t>Surface Studio / Hub 系列</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>Surface Studio 2</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>Surface Studio 2</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>第 2 代 (2018) (2018)</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>历史机型</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>商用专属 (For Business)</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>29,888 起</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
+        <is>
+          <t>28.0 英寸 PixelSense™ 巨幅触控显示屏 | 4500 × 3000 (1350 万像素) | 60Hz (真实比例 13.5 亿色超薄 IPS 显示屏)</t>
+        </is>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
+        <is>
+          <t>Intel® 第 7 代酷睿™ i7-7820HQ</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="M47" s="20" t="inlineStr">
+        <is>
+          <t>16GB / 32GB DDR4 (2400 MT/s) | 1TB / 2TB PCIe NVMe SSD</t>
+        </is>
+      </c>
+      <c r="N47" s="20" t="inlineStr">
+        <is>
+          <t>持续交流电源连接</t>
+        </is>
+      </c>
+      <c r="O47" s="20" t="inlineStr">
+        <is>
+          <t>9560g (9.56 kg)</t>
+        </is>
+      </c>
+      <c r="P47" s="20" t="inlineStr">
+        <is>
+          <t>配备 Surface 蓝牙键盘与精准鼠标 | 笔协议: 10 点触控，支持 Surface 触控笔 (4096级压感) 与 Surface Dial</t>
+        </is>
+      </c>
+      <c r="Q47" s="20" t="inlineStr">
+        <is>
+          <t>4 × USB-A 3.0 + 1 × USB-C + 千兆以太网口 + SD 卡槽; 雷电: 否; 磁吸: not_applicable</t>
+        </is>
+      </c>
+      <c r="R47" s="23" t="inlineStr">
+        <is>
+          <t>点击进入商城选配 ↗</t>
+        </is>
+      </c>
+      <c r="S47" s="23" t="inlineStr">
+        <is>
+          <t>点击查阅架构白皮书 ↗</t>
+        </is>
+      </c>
+      <c r="T47" s="20" t="inlineStr">
+        <is>
+          <t>microsoft_official</t>
+        </is>
+      </c>
+      <c r="U47" s="21" t="inlineStr">
+        <is>
+          <t>✅ 100% 官方已核验</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>Surface Studio / Hub 系列</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>Surface Studio 初代 (Original)</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>Surface Studio (1st Gen)</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E48" s="19" t="inlineStr">
         <is>
           <t>初代 (2016) (2016)</t>
         </is>
       </c>
-      <c r="F45" s="19" t="inlineStr">
+      <c r="F48" s="26" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G48" s="19" t="inlineStr">
         <is>
           <t>商用专属 (For Business)</t>
         </is>
       </c>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="H48" s="22" t="inlineStr">
         <is>
           <t>25,888 起</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I48" s="20" t="inlineStr">
         <is>
           <t>亮铂金</t>
         </is>
       </c>
-      <c r="J45" s="10" t="inlineStr">
+      <c r="J48" s="20" t="inlineStr">
         <is>
           <t>28.0 英寸 PixelSense™ 巨幕触控屏 | 4500 × 3000 (1350 万像素) | 60Hz (真实比例超薄触控 IPS 面板)</t>
         </is>
       </c>
-      <c r="K45" s="10" t="inlineStr">
+      <c r="K48" s="20" t="inlineStr">
         <is>
           <t>Intel® 第 6 代酷睿™ i5-6440HQ / i7-6700HQ</t>
         </is>
       </c>
-      <c r="L45" s="10" t="inlineStr">
+      <c r="L48" s="20" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M45" s="10" t="inlineStr">
+      <c r="M48" s="20" t="inlineStr">
         <is>
           <t>8GB / 16GB / 32GB DDR4 | 64GB SSD + 1TB / 2TB 混合双硬盘 (RapidDrive)</t>
         </is>
       </c>
-      <c r="N45" s="10" t="inlineStr">
+      <c r="N48" s="20" t="inlineStr">
         <is>
           <t>持续交流电源连接</t>
         </is>
       </c>
-      <c r="O45" s="10" t="inlineStr">
+      <c r="O48" s="20" t="inlineStr">
         <is>
           <t>9560g (9.56 kg)</t>
         </is>
       </c>
-      <c r="P45" s="10" t="inlineStr">
+      <c r="P48" s="20" t="inlineStr">
         <is>
           <t>配赠 Surface 蓝牙键盘与无线鼠标 | 笔协议: 10 点触控，配备 Surface Pen 与 Surface Dial 屏上直接拾色器</t>
         </is>
       </c>
-      <c r="Q45" s="10" t="inlineStr">
+      <c r="Q48" s="20" t="inlineStr">
         <is>
           <t>4 × USB-A 3.0 + Mini DisplayPort + 千兆网口 + SD 卡槽; 雷电: 否; 磁吸: not_applicable</t>
         </is>
       </c>
-      <c r="R45" s="13" t="inlineStr">
+      <c r="R48" s="23" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S45" s="13" t="inlineStr">
+      <c r="S48" s="23" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T45" s="10" t="inlineStr">
+      <c r="T48" s="20" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U45" s="11" t="inlineStr">
+      <c r="U48" s="21" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Surface Studio / Hub 系列</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>Surface Hub 2S (50" / 85")</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr">
         <is>
           <t>Surface Hub 2S</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>Hub 2S (2019/2021) (2019)</t>
         </is>
       </c>
-      <c r="F46" s="19" t="inlineStr">
+      <c r="F49" s="26" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G49" s="19" t="inlineStr">
         <is>
           <t>商用专属 (For Business)</t>
         </is>
       </c>
-      <c r="H46" s="12" t="inlineStr">
+      <c r="H49" s="22" t="inlineStr">
         <is>
           <t>72,088 起</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>亮铂金巨幕金属边框</t>
-        </is>
-      </c>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>50.0 英寸 / 85.0 英寸 PixelSense™ 巨幅交互屏 | 3840 × 2560 (50 英寸 4K+ 3:2) | 60Hz (IPS 触控防眩光显示面板)</t>
         </is>
       </c>
-      <c r="K46" s="10" t="inlineStr">
+      <c r="K49" s="20" t="inlineStr">
         <is>
           <t>Intel® 第 8 代酷睿™ i5-8350U 四核</t>
         </is>
       </c>
-      <c r="L46" s="10" t="inlineStr">
+      <c r="L49" s="20" t="inlineStr">
         <is>
           <t>not_applicable</t>
         </is>
       </c>
-      <c r="M46" s="10" t="inlineStr">
+      <c r="M49" s="20" t="inlineStr">
         <is>
           <t>16GB DDR4 | 128GB M.2 SSD</t>
         </is>
       </c>
-      <c r="N46" s="10" t="inlineStr">
+      <c r="N49" s="20" t="inlineStr">
         <is>
           <t>市电直供 (可选移动电池包)</t>
         </is>
       </c>
-      <c r="O46" s="10" t="inlineStr">
+      <c r="O49" s="20" t="inlineStr">
         <is>
           <t>28000g (28 kg 巨幕白板)</t>
         </is>
       </c>
-      <c r="P46" s="10" t="inlineStr">
+      <c r="P49" s="20" t="inlineStr">
         <is>
           <t>支持标准蓝牙无线键鼠 | 笔协议: 原生多点触控与支持双笔同步书写 (Surface Hub 2 Pen)</t>
         </is>
       </c>
-      <c r="Q46" s="10" t="inlineStr">
+      <c r="Q49" s="20" t="inlineStr">
         <is>
           <t>4 × USB-C + 1 × USB-A + HDMI 输入 + Mini-DP + 千兆 RJ45; 雷电: 否; 磁吸: not_applicable</t>
         </is>
       </c>
-      <c r="R46" s="13" t="inlineStr">
+      <c r="R49" s="23" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S46" s="13" t="inlineStr">
+      <c r="S49" s="23" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T46" s="10" t="inlineStr">
+      <c r="T49" s="20" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U46" s="11" t="inlineStr">
+      <c r="U49" s="21" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="14" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="14" t="inlineStr">
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>Surface Duo 系列</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>Surface Duo 初代 (Original)</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>Surface Duo (1st Gen)</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E50" s="14" t="inlineStr">
         <is>
           <t>初代 (2020) (2020)</t>
         </is>
       </c>
-      <c r="F47" s="26" t="inlineStr">
+      <c r="F50" s="24" t="inlineStr">
         <is>
           <t>历史机型</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>消费级零售</t>
         </is>
       </c>
-      <c r="H47" s="17" t="inlineStr">
+      <c r="H50" s="17" t="inlineStr">
         <is>
           <t>9,988 起</t>
         </is>
       </c>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>冰川白</t>
         </is>
       </c>
-      <c r="J47" s="15" t="inlineStr">
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t>双 5.6 英寸 AMOLED 展开为 8.1 英寸 | 展开 2700 × 1800 | 60Hz (双 AMOLED 柔性基底硬屏)</t>
         </is>
       </c>
-      <c r="K47" s="15" t="inlineStr">
+      <c r="K50" s="15" t="inlineStr">
         <is>
           <t>高通骁龙™ 855 移动平台</t>
         </is>
       </c>
-      <c r="L47" s="15" t="inlineStr">
+      <c r="L50" s="15" t="inlineStr">
         <is>
           <t>7 TOPS</t>
         </is>
       </c>
-      <c r="M47" s="15" t="inlineStr">
+      <c r="M50" s="15" t="inlineStr">
         <is>
           <t>6GB LPDDR4x | 128GB / 256GB UFS 3.0</t>
         </is>
       </c>
-      <c r="N47" s="15" t="inlineStr">
+      <c r="N50" s="15" t="inlineStr">
         <is>
           <t>长达 15.5 小时本地视频播放</t>
         </is>
       </c>
-      <c r="O47" s="15" t="inlineStr">
+      <c r="O50" s="15" t="inlineStr">
         <is>
           <t>250g (极其超薄)</t>
         </is>
       </c>
-      <c r="P47" s="15" t="inlineStr">
+      <c r="P50" s="15" t="inlineStr">
         <is>
           <t>屏幕虚拟键盘或外接蓝牙键盘 | 笔协议: 支持 Surface Slim Pen 手写笔双屏批注</t>
         </is>
       </c>
-      <c r="Q47" s="15" t="inlineStr">
+      <c r="Q50" s="15" t="inlineStr">
         <is>
           <t>1 × USB-C 3.1 Gen 2; 雷电: 否; 磁吸: not_applicable</t>
         </is>
       </c>
-      <c r="R47" s="18" t="inlineStr">
+      <c r="R50" s="18" t="inlineStr">
         <is>
           <t>点击进入商城选配 ↗</t>
         </is>
       </c>
-      <c r="S47" s="18" t="inlineStr">
+      <c r="S50" s="18" t="inlineStr">
         <is>
           <t>点击查阅架构白皮书 ↗</t>
         </is>
       </c>
-      <c r="T47" s="15" t="inlineStr">
+      <c r="T50" s="15" t="inlineStr">
         <is>
           <t>microsoft_official</t>
         </is>
       </c>
-      <c r="U47" s="16" t="inlineStr">
+      <c r="U50" s="16" t="inlineStr">
         <is>
           <t>✅ 100% 官方已核验</t>
         </is>
@@ -5346,6 +5661,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R47" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R48" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R49" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R50" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5357,7 +5678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5452,434 +5773,620 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Surface Pro 13 英寸 (第 12 代)</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>双平台 AI PC 旗舰：可选英特尔酷睿 Ultra (第3代) 或高通骁龙 X2 平台</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>¥15,488 起 (骁龙版) / ¥16,888 起 (Intel Ultra 版)</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>双平台架构：英特尔® 酷睿™ Ultra 5 / Ultra 7 (第 3 代) 或 高通骁龙® X2</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>50 TOPS (Intel) / 80 TOPS (骁龙)</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>13.0 英寸 PixelSense™ Flow (2880 × 1920, 双层串联 OLED (Ultra 7 / 骁龙版标配) / 防反射超清 LCD (Ultra 5 配备))</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>亮铂金、典雅黑、沙漫金</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Surface Pro 13 英寸 (第 12 代) 商用版 - Intel 版</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>商用 AI PC 旗舰：搭载英特尔® 酷睿™ Ultra (第 3 代) 处理器，50 TOPS 端侧 AI 算力与防眩光 LCD/双层串联 OLED 屏幕</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>¥16,888 起 (商用)</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>英特尔® 酷睿™ Ultra 5 / Ultra 7 处理器 (第 3 代)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>50 TOPS</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>13.0 英寸 PixelSense™ Flow (2880 × 1920, 防反射超清 LCD (Ultra 5) / 双层串联 OLED (Ultra 7))</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Surface Pro 第 12 代专业键盘盖 / Surface Pro Flex 无线键盘 (集成笔槽充电)</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>常规办公约 15 小时</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>895g (OLED 版) / 885g (LCD 版)</t>
         </is>
       </c>
-      <c r="K5" s="18" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>打开 Intel 选配页 ↗</t>
         </is>
       </c>
-      <c r="L5" s="18" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>打开骁龙选配页 ↗</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Surface Pro 13 英寸 (第 12 代) 商用版 - 骁龙版</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>商用 ARM AI PC 巅峰：搭载高通骁龙 X2 (Snapdragon® X2 Elite 处理器)，80 TOPS 巅峰 AI 算力与双层串联 OLED 屏幕</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>¥15,488 起 (商用)</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>高通骁龙 X2 (Snapdragon® X2 Elite 处理器) (12 核心)</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>80 TOPS</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>13.0 英寸 PixelSense™ Flow (2880 × 1920, 双层串联 OLED (Tandem OLED))</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>Surface Pro 第 12 代专业键盘盖 / Surface Pro Flex 无线键盘 (集成笔槽充电)</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>常规办公约 15 小时</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>895g (OLED 版) / 885g (LCD 版)</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>打开 Intel 选配页 ↗</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>打开骁龙选配页 ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Surface Pro, 12 英寸 (第 1 代)</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>12 英寸便携羽量级 Copilot+ PC，高通骁龙 X Plus 8 核</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>¥6,788 起</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>¥7,888 起 (消费版)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>高通骁龙 X Plus (8 核心 X1P-42-100)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>45 TOPS</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>12.0 英寸 PixelSense™ 触控屏 (2196 × 1464, PixelSense™ LCD 高清触控屏)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>亮铂金、罗兰紫、碧海青</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Surface Pro 12 英寸特制版专业键盘 (碧海青 / 板岩灰 / 罗兰紫三色可选)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>686 克 (超轻量羽量级设计)</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>打开 Intel 选配页 ↗</t>
         </is>
       </c>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>打开骁龙选配页 ↗</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 10 商用版</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Intel Core Ultra 架构商用先锋，专用 NFC 登录</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>9,888 起 (商用)</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Intel® Core™ Ultra 5 135U / Ultra 7 165U</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>11.5 TOPS</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>13.0 英寸 PixelSense™ Flow (2880 × 1920, 抗反射防眩光防指纹涂层 LCD)</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>亮铂金、典黑</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>Surface Pro 特制版键盘盖 (带 NFC 安全卡识别)</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>日常办公最长 19 小时</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>879g</t>
         </is>
       </c>
-      <c r="K7" s="18" t="inlineStr">
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>打开 Intel 选配页 ↗</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Surface Laptop 13.8 英寸 (第 8 代)</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>双平台触觉触控轻薄本：可选英特尔酷睿 Ultra (第3代) 或高通骁龙 X2 平台</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>¥14,888 起 (骁龙版) / ¥16,888 起 (Intel Ultra 版)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>双平台架构：英特尔® 酷睿™ Ultra 5 / Ultra 7 (第 3 代) 或 高通骁龙® X2</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>50 TOPS (Intel) / 80 TOPS (骁龙)</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop 13.8 英寸 (第 8 代) 商用版 - Intel 版</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>商用轻薄触控本旗舰：搭载英特尔® 酷睿™ Ultra (第 3 代) 处理器，50 TOPS AI 算力与全域触觉触控板</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>¥16,888 起 (商用)</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>英特尔® 酷睿™ Ultra 5 / Ultra 7 处理器 (第 3 代)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>50 TOPS</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>13.8 英寸 PixelSense™ Flow (2304 × 1536, 超清圆角窄边框触控屏)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>亮铂金、典黑、宝石蓝、沙漫金</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>一体化精密铝合金 C 面集成触觉反馈触控板 (不支持触控笔)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>1340 克</t>
         </is>
       </c>
-      <c r="K8" s="24" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>打开 Intel 选配页 ↗</t>
         </is>
       </c>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>打开骁龙选配页 ↗</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Surface Laptop 15 英寸 (第 8 代)</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>双平台 15 英寸巨幕商务轻薄本：可选英特尔酷睿 Ultra (第3代) 或高通骁龙 X2</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>¥16,888 起 (Intel Ultra 版) / ¥15,888 起 (骁龙版)</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>双平台架构：英特尔® 酷睿™ Ultra 5 / Ultra 7 (第 3 代) 或 高通骁龙® X2</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>50 TOPS (Intel) / 80 TOPS (骁龙)</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Surface Laptop 13.8 英寸 (第 8 代) 商用版 - 骁龙版</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>商用轻薄本续航巅峰：搭载高通骁龙 X2 (Snapdragon® X2 Elite 处理器)，80 TOPS 巅峰 AI 算力与 20 小时续航</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>¥14,888 起 (商用)</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>高通骁龙 X2 (Snapdragon® X2 Elite 处理器) (12 核心)</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>80 TOPS</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>13.8 英寸 PixelSense™ Flow (2304 × 1536, 超清圆角窄边框触控屏)</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>一体化精密铝合金 C 面集成触觉反馈触控板 (不支持触控笔)</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>1340 克</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>打开 Intel 选配页 ↗</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>打开骁龙选配页 ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop 15 英寸 (第 8 代) 商用版 - Intel 版</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>商用大屏性能轻薄本：搭载英特尔® 酷睿™ Ultra X7 (第 3 代) 处理器，50 TOPS AI 与 15 英寸巨幕</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>¥18,888 起 (商用)</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>英特尔® 酷睿™ Ultra X7 处理器 (第 3 代)</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>50 TOPS</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>15.0 英寸 PixelSense™ Flow (2496 × 1664, 超视网膜 LCD)</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>一体化精密铝合金 C 面集成触觉反馈触控板 (不支持触控笔)</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>常规办公长达 18 小时</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>1660g (1.66 kg)</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>打开 Intel 选配页 ↗</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>打开骁龙选配页 ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Surface Laptop 15 英寸 (第 8 代) 商用版 - 骁龙版</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>商用大屏续航巅峰：搭载高通骁龙 X2 (Snapdragon® X2 Elite 处理器)，80 TOPS AI 与 22 小时超长续航</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>¥16,888 起 (商用)</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>高通骁龙 X2 (Snapdragon® X2 Elite 处理器) (12 核心)</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>80 TOPS</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>15.0 英寸 PixelSense™ Flow (2496 × 1664, 超视网膜 LCD)</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>亮铂金、典雅黑</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>一体化精密铝合金 C 面集成触觉反馈触控板 (不支持触控笔)</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>常规办公长达 18 小时</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>1660g (1.66 kg)</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>打开 Intel 选配页 ↗</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>打开骁龙选配页 ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Surface Laptop 6 商用版 (13.5" &amp; 15")</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra H 系列标压商用野兽，内置智能卡读卡器</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>9,988 起</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Intel® Core™ Ultra 5 135H / Ultra 7 165H</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>11.5 TOPS</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>13.5 英寸 / 15.0 英寸 PixelSense™ (2256 × 1504 (13.5") / 2496 × 1664 (15"), 防眩光抗反射涂层 LCD)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>亮铂金、典黑</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>一体化精密铝合金 C 面集成触觉反馈触控板 (不支持触控笔)</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>常规办公长达 18 小时</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>1660g (1.66 kg)</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>传统磨砂抗指纹轻薄本键盘 (可选智能卡读卡器)</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>长达 18.5 ~ 19 小时</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>1380g (13.5") / 1680g (15")</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>打开 Intel 选配页 ↗</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>打开骁龙选配页 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Surface Laptop 6 商用版 (13.5" &amp; 15")</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>Intel Core Ultra H 系列标压商用野兽，内置智能卡读卡器</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>9,988 起</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>Intel® Core™ Ultra 5 135H / Ultra 7 165H</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>11.5 TOPS</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>13.5 英寸 / 15.0 英寸 PixelSense™ (2256 × 1504 (13.5") / 2496 × 1664 (15"), 防眩光抗反射涂层 LCD)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>亮铂金、典黑</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>传统磨砂抗指纹轻薄本键盘 (可选智能卡读卡器)</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>长达 18.5 ~ 19 小时</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>1380g (13.5") / 1680g (15")</t>
-        </is>
-      </c>
-      <c r="K10" s="24" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Surface Go 4 商用版</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>521g 极致羽量级二合一，四核 Intel N200 生产力飞跃</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>4,588 起</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Intel® 处理器 N200</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>10.5 英寸 PixelSense™ 显示屏 (1920 × 1280, 康宁大猩猩玻璃 3 LCD)</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>亮铂金</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Surface Go 专业特制键盘盖 (亮铂金 / 典黑)</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>典型日常使用长达 12.5 小时</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>521g (羽量级口袋平板)</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t>打开 Intel 选配页 ↗</t>
         </is>
       </c>
-      <c r="L10" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Surface Go 4 商用版</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>521g 极致羽量级二合一，四核 Intel N200 生产力飞跃</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>4,588 起</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Intel® 处理器 N200</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>10.5 英寸 PixelSense™ 显示屏 (1920 × 1280, 康宁大猩猩玻璃 3 LCD)</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>亮铂金</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>Surface Go 专业特制键盘盖 (亮铂金 / 典黑)</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>典型日常使用长达 12.5 小时</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
-        <is>
-          <t>521g (羽量级口袋平板)</t>
-        </is>
-      </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>打开 Intel 选配页 ↗</t>
-        </is>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5896,12 +6403,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
